--- a/Plantilla_Gestion_Requerimientos_Scrum.xlsx
+++ b/Plantilla_Gestion_Requerimientos_Scrum.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxii\Downloads\JugueteriaFullStack_II-Trabajo-17-09-26\JugueteriaFullStack_II-Trabajo-17-09-26\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DF662F-E401-4C7E-87B1-AC2A75470F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Epicas" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Historias de Usuario" sheetId="2" r:id="rId6"/>
+    <sheet name="Epicas" sheetId="1" r:id="rId1"/>
+    <sheet name="Historias de Usuario" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -2168,40 +2177,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="7">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
@@ -2212,7 +2224,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2234,129 +2246,186 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="21">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC1E4F5"/>
-          <bgColor rgb="FFC1E4F5"/>
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9EAD3"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -2381,128 +2450,140 @@
       </border>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FFFFF2CC"/>
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Epicas-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Epicas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Historias de Usuario-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Historias de Usuario-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H98" displayName="TablaEpicas" name="TablaEpicas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEpicas" displayName="TablaEpicas" ref="A1:H98">
   <tableColumns count="8">
-    <tableColumn name="ID" id="1"/>
-    <tableColumn name="Épica" id="2"/>
-    <tableColumn name="Descripción" id="3"/>
-    <tableColumn name="Objetivo/Valor" id="4"/>
-    <tableColumn name="Prioridad" id="5"/>
-    <tableColumn name="Estado" id="6"/>
-    <tableColumn name="Responsable" id="7"/>
-    <tableColumn name="Observaciones" id="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Épica"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Descripción"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Objetivo/Valor"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Prioridad"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estado"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Responsable"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Epicas-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Epicas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M201" displayName="TablaHistoriasUsuario" name="TablaHistoriasUsuario" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaHistoriasUsuario" displayName="TablaHistoriasUsuario" ref="A1:M201">
   <tableColumns count="13">
-    <tableColumn name="¿" id="1"/>
-    <tableColumn name="Épica" id="2"/>
-    <tableColumn name="Historia" id="3"/>
-    <tableColumn name="Como" id="4"/>
-    <tableColumn name="Quiero" id="5"/>
-    <tableColumn name="Para" id="6"/>
-    <tableColumn name="Prioridad" id="7"/>
-    <tableColumn name="Sprint" id="8"/>
-    <tableColumn name="Criterio de Aceptación" id="9"/>
-    <tableColumn name="Estado" id="10"/>
-    <tableColumn name="Review" id="11"/>
-    <tableColumn name="Responsable" id="12"/>
-    <tableColumn name="Observaciones" id="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="¿"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Épica"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Historia"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Como"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Quiero"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Para"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Prioridad"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Sprint"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Criterio de Aceptación"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Estado"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Review"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Responsable"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Historias de Usuario-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Historias de Usuario-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2692,28 +2773,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="3" width="43.88"/>
-    <col customWidth="1" min="4" max="4" width="43.13"/>
-    <col customWidth="1" min="5" max="5" width="14.0"/>
-    <col customWidth="1" min="6" max="6" width="18.0"/>
-    <col customWidth="1" min="7" max="7" width="22.0"/>
-    <col customWidth="1" min="8" max="8" width="34.0"/>
-    <col customWidth="1" min="9" max="26" width="8.75"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="43.8984375" customWidth="1"/>
+    <col min="4" max="4" width="43.09765625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="26" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
+    <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2739,9 +2820,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="28.5" customHeight="1">
+    <row r="2" spans="1:8" ht="28.5" customHeight="1">
       <c r="A2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
@@ -2758,16 +2839,16 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="28.5" customHeight="1">
+    <row r="3" spans="1:8" ht="28.5" customHeight="1">
       <c r="A3" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -2784,14 +2865,14 @@
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="28.5" customHeight="1">
+    <row r="4" spans="1:8" ht="28.5" customHeight="1">
       <c r="A4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>19</v>
@@ -2808,14 +2889,14 @@
       <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="28.5" customHeight="1">
+    <row r="5" spans="1:8" ht="28.5" customHeight="1">
       <c r="A5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>24</v>
@@ -2832,14 +2913,14 @@
       <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" ht="28.5" customHeight="1">
+    <row r="6" spans="1:8" ht="28.5" customHeight="1">
       <c r="A6" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>28</v>
@@ -2856,14 +2937,14 @@
       <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="28.5" customHeight="1">
+    <row r="7" spans="1:8" ht="28.5" customHeight="1">
       <c r="A7" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>33</v>
@@ -2880,14 +2961,14 @@
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" ht="28.5" customHeight="1">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1">
       <c r="A8" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>37</v>
@@ -2895,7 +2976,7 @@
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -2904,14 +2985,14 @@
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="28.5" customHeight="1">
+    <row r="9" spans="1:8" ht="28.5" customHeight="1">
       <c r="A9" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>41</v>
@@ -2928,14 +3009,14 @@
       <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>45</v>
@@ -2952,14 +3033,14 @@
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" ht="28.5" customHeight="1">
+    <row r="11" spans="1:8" ht="28.5" customHeight="1">
       <c r="A11" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>49</v>
@@ -2976,14 +3057,14 @@
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" ht="28.5" customHeight="1">
+    <row r="12" spans="1:8" ht="28.5" customHeight="1">
       <c r="A12" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>53</v>
@@ -3000,14 +3081,14 @@
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" ht="28.5" customHeight="1">
+    <row r="13" spans="1:8" ht="28.5" customHeight="1">
       <c r="A13" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>57</v>
@@ -3024,14 +3105,14 @@
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" ht="28.5" customHeight="1">
+    <row r="14" spans="1:8" ht="28.5" customHeight="1">
       <c r="A14" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>61</v>
@@ -3048,14 +3129,14 @@
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" ht="28.5" customHeight="1">
+    <row r="15" spans="1:8" ht="28.5" customHeight="1">
       <c r="A15" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>65</v>
@@ -3072,14 +3153,14 @@
       <c r="F15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" ht="28.5" customHeight="1">
+    <row r="16" spans="1:8" ht="28.5" customHeight="1">
       <c r="A16" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>69</v>
@@ -3096,14 +3177,14 @@
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" ht="28.5" customHeight="1">
+    <row r="17" spans="1:26" ht="28.5" customHeight="1">
       <c r="A17" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>73</v>
@@ -3120,22 +3201,22 @@
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" ht="28.5" customHeight="1">
+    <row r="18" spans="1:26" ht="28.5" customHeight="1">
       <c r="A18" s="3">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -3144,34 +3225,34 @@
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-    </row>
-    <row r="19" ht="28.5" customHeight="1">
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+    </row>
+    <row r="19" spans="1:26" ht="28.5" customHeight="1">
       <c r="A19" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -3186,1083 +3267,1083 @@
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-    </row>
-    <row r="20" ht="28.5" customHeight="1">
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+    </row>
+    <row r="20" spans="1:26" ht="28.5" customHeight="1">
       <c r="A20" s="3"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-    </row>
-    <row r="21" ht="28.5" customHeight="1">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+    </row>
+    <row r="21" spans="1:26" ht="28.5" customHeight="1">
       <c r="A21" s="3"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
-    </row>
-    <row r="22" ht="28.5" customHeight="1">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+    </row>
+    <row r="22" spans="1:26" ht="28.5" customHeight="1">
       <c r="A22" s="3"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-    </row>
-    <row r="23" ht="28.5" customHeight="1">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+    </row>
+    <row r="23" spans="1:26" ht="28.5" customHeight="1">
       <c r="A23" s="3"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-    </row>
-    <row r="24" ht="28.5" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
-    </row>
-    <row r="25" ht="28.5" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-    </row>
-    <row r="26" ht="28.5" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-    </row>
-    <row r="27" ht="28.5" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-    </row>
-    <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-    </row>
-    <row r="29" ht="28.5" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-    </row>
-    <row r="30" ht="28.5" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-    </row>
-    <row r="31" ht="28.5" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-    </row>
-    <row r="32" ht="28.5" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-    </row>
-    <row r="33" ht="28.5" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-    </row>
-    <row r="34" ht="28.5" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" ht="28.5" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" ht="28.5" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" ht="28.5" customHeight="1">
-      <c r="A37" s="12"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" ht="28.5" customHeight="1">
-      <c r="A38" s="12"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" ht="28.5" customHeight="1">
-      <c r="A39" s="12"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" ht="28.5" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" s="12"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="11"/>
-    </row>
-    <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="11"/>
-    </row>
-    <row r="43" ht="28.5" customHeight="1">
-      <c r="A43" s="12"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" ht="28.5" customHeight="1">
-      <c r="A44" s="12"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" s="12"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" ht="28.5" customHeight="1">
-      <c r="A46" s="12"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" ht="28.5" customHeight="1">
-      <c r="A47" s="12"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" ht="28.5" customHeight="1">
-      <c r="A48" s="12"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" ht="28.5" customHeight="1">
-      <c r="A49" s="12"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" ht="28.5" customHeight="1">
-      <c r="A50" s="12"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" ht="28.5" customHeight="1">
-      <c r="A51" s="12"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" ht="28.5" customHeight="1">
-      <c r="A52" s="12"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="11"/>
-    </row>
-    <row r="53" ht="28.5" customHeight="1">
-      <c r="A53" s="12"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" ht="28.5" customHeight="1">
-      <c r="A54" s="12"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="11"/>
-    </row>
-    <row r="55" ht="28.5" customHeight="1">
-      <c r="A55" s="12"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="11"/>
-    </row>
-    <row r="56" ht="28.5" customHeight="1">
-      <c r="A56" s="12"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="11"/>
-    </row>
-    <row r="57" ht="28.5" customHeight="1">
-      <c r="A57" s="12"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="11"/>
-    </row>
-    <row r="58" ht="28.5" customHeight="1">
-      <c r="A58" s="12"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="11"/>
-    </row>
-    <row r="59" ht="28.5" customHeight="1">
-      <c r="A59" s="12"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="11"/>
-    </row>
-    <row r="60" ht="28.5" customHeight="1">
-      <c r="A60" s="12"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="11"/>
-    </row>
-    <row r="61" ht="28.5" customHeight="1">
-      <c r="A61" s="12"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="11"/>
-    </row>
-    <row r="62" ht="28.5" customHeight="1">
-      <c r="A62" s="12"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="11"/>
-    </row>
-    <row r="63" ht="28.5" customHeight="1">
-      <c r="A63" s="12"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="11"/>
-    </row>
-    <row r="64" ht="28.5" customHeight="1">
-      <c r="A64" s="12"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="11"/>
-    </row>
-    <row r="65" ht="28.5" customHeight="1">
-      <c r="A65" s="12"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="11"/>
-    </row>
-    <row r="66" ht="28.5" customHeight="1">
-      <c r="A66" s="12"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="11"/>
-    </row>
-    <row r="67" ht="28.5" customHeight="1">
-      <c r="A67" s="12"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="11"/>
-    </row>
-    <row r="68" ht="28.5" customHeight="1">
-      <c r="A68" s="12"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="11"/>
-    </row>
-    <row r="69" ht="28.5" customHeight="1">
-      <c r="A69" s="12"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="11"/>
-    </row>
-    <row r="70" ht="28.5" customHeight="1">
-      <c r="A70" s="12"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="11"/>
-    </row>
-    <row r="71" ht="28.5" customHeight="1">
-      <c r="A71" s="12"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="11"/>
-    </row>
-    <row r="72" ht="28.5" customHeight="1">
-      <c r="A72" s="12"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="11"/>
-    </row>
-    <row r="73" ht="28.5" customHeight="1">
-      <c r="A73" s="12"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="11"/>
-    </row>
-    <row r="74" ht="28.5" customHeight="1">
-      <c r="A74" s="12"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="11"/>
-    </row>
-    <row r="75" ht="28.5" customHeight="1">
-      <c r="A75" s="12"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="11"/>
-    </row>
-    <row r="76" ht="28.5" customHeight="1">
-      <c r="A76" s="12"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="11"/>
-    </row>
-    <row r="77" ht="28.5" customHeight="1">
-      <c r="A77" s="12"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="11"/>
-    </row>
-    <row r="78" ht="28.5" customHeight="1">
-      <c r="A78" s="12"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="11"/>
-    </row>
-    <row r="79" ht="28.5" customHeight="1">
-      <c r="A79" s="12"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="11"/>
-    </row>
-    <row r="80" ht="28.5" customHeight="1">
-      <c r="A80" s="12"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="11"/>
-    </row>
-    <row r="81" ht="28.5" customHeight="1">
-      <c r="A81" s="12"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="11"/>
-    </row>
-    <row r="82" ht="28.5" customHeight="1">
-      <c r="A82" s="12"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="11"/>
-    </row>
-    <row r="83" ht="28.5" customHeight="1">
-      <c r="A83" s="12"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="11"/>
-    </row>
-    <row r="84" ht="28.5" customHeight="1">
-      <c r="A84" s="12"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="11"/>
-    </row>
-    <row r="85" ht="28.5" customHeight="1">
-      <c r="A85" s="12"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="11"/>
-    </row>
-    <row r="86" ht="28.5" customHeight="1">
-      <c r="A86" s="12"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="11"/>
-    </row>
-    <row r="87" ht="28.5" customHeight="1">
-      <c r="A87" s="12"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="11"/>
-    </row>
-    <row r="88" ht="28.5" customHeight="1">
-      <c r="A88" s="12"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="11"/>
-    </row>
-    <row r="89" ht="28.5" customHeight="1">
-      <c r="A89" s="12"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="11"/>
-    </row>
-    <row r="90" ht="28.5" customHeight="1">
-      <c r="A90" s="12"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="11"/>
-    </row>
-    <row r="91" ht="28.5" customHeight="1">
-      <c r="A91" s="12"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="11"/>
-    </row>
-    <row r="92" ht="28.5" customHeight="1">
-      <c r="A92" s="12"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="11"/>
-    </row>
-    <row r="93" ht="28.5" customHeight="1">
-      <c r="A93" s="12"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="11"/>
-    </row>
-    <row r="94" ht="28.5" customHeight="1">
-      <c r="A94" s="12"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="11"/>
-    </row>
-    <row r="95" ht="28.5" customHeight="1">
-      <c r="A95" s="12"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="11"/>
-    </row>
-    <row r="96" ht="28.5" customHeight="1">
-      <c r="A96" s="12"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="11"/>
-    </row>
-    <row r="97" ht="28.5" customHeight="1">
-      <c r="A97" s="12"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="11"/>
-    </row>
-    <row r="98" ht="28.5" customHeight="1">
-      <c r="A98" s="12"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="11"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1"/>
-    <row r="100" ht="13.5" customHeight="1"/>
-    <row r="101" ht="13.5" customHeight="1"/>
-    <row r="102" ht="13.5" customHeight="1"/>
-    <row r="103" ht="13.5" customHeight="1"/>
-    <row r="104" ht="13.5" customHeight="1"/>
-    <row r="105" ht="13.5" customHeight="1"/>
-    <row r="106" ht="13.5" customHeight="1"/>
-    <row r="107" ht="13.5" customHeight="1"/>
-    <row r="108" ht="13.5" customHeight="1"/>
-    <row r="109" ht="13.5" customHeight="1"/>
-    <row r="110" ht="13.5" customHeight="1"/>
-    <row r="111" ht="13.5" customHeight="1"/>
-    <row r="112" ht="13.5" customHeight="1"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+    </row>
+    <row r="24" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+    </row>
+    <row r="25" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+    </row>
+    <row r="26" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+    </row>
+    <row r="27" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+    </row>
+    <row r="28" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+    </row>
+    <row r="29" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+    </row>
+    <row r="30" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+    </row>
+    <row r="31" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+    </row>
+    <row r="32" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+    </row>
+    <row r="33" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+    </row>
+    <row r="34" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A47" s="3"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:26" ht="28.5" customHeight="1">
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A49" s="3"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A50" s="3"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A51" s="3"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A75" s="3"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A82" s="3"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A83" s="3"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A84" s="3"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A85" s="3"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A86" s="3"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A87" s="3"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A88" s="3"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A90" s="3"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A91" s="3"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A92" s="3"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A93" s="3"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A94" s="3"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A95" s="3"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A96" s="3"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A98" s="3"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="100" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="101" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="102" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="103" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="104" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="105" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="106" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="107" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="108" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="109" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="110" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="111" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="112" spans="1:8" ht="13.5" customHeight="1"/>
     <row r="113" ht="13.5" customHeight="1"/>
     <row r="114" ht="13.5" customHeight="1"/>
     <row r="115" ht="13.5" customHeight="1"/>
@@ -5150,73 +5231,63 @@
     <row r="997" ht="13.5" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="E2:E98">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>E2="Alta"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E98">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>E2="Media"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E98">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>E2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F98">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>F2="Finalizada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F98">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>F2="Bloqueada"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G98">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G98" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Brandon Cantero,Maximiliano Ojeda,Gustavo Cisternas"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E98">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E98" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F98">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F98" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Pendiente,En análisis,Lista,En desarrollo,En revisión,Finalizada,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="30.0"/>
-    <col customWidth="1" min="4" max="4" width="24.0"/>
-    <col customWidth="1" min="5" max="6" width="32.0"/>
-    <col customWidth="1" min="7" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="9" width="38.0"/>
-    <col customWidth="1" min="10" max="10" width="18.0"/>
-    <col customWidth="1" min="11" max="11" width="20.0"/>
-    <col customWidth="1" min="12" max="12" width="22.0"/>
-    <col customWidth="1" min="13" max="13" width="34.0"/>
-    <col customWidth="1" min="14" max="26" width="8.75"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="32" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="14" max="26" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.0" customHeight="1">
+    <row r="1" spans="1:13" ht="27" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -5257,7 +5328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="33.0" customHeight="1">
+    <row r="2" spans="1:13" ht="33" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>92</v>
       </c>
@@ -5280,7 +5351,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>97</v>
@@ -5291,12 +5362,12 @@
       <c r="K2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="11"/>
+      <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" ht="33.0" customHeight="1">
+    <row r="3" spans="1:13" ht="33" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>99</v>
       </c>
@@ -5318,7 +5389,7 @@
       <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="12"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
         <v>103</v>
       </c>
@@ -5328,12 +5399,12 @@
       <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" ht="33.0" customHeight="1">
+    <row r="4" spans="1:13" ht="33" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>105</v>
       </c>
@@ -5355,7 +5426,7 @@
       <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="12"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
         <v>109</v>
       </c>
@@ -5365,12 +5436,12 @@
       <c r="K4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" ht="33.0" customHeight="1">
+    <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>111</v>
       </c>
@@ -5392,7 +5463,7 @@
       <c r="G5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
         <v>115</v>
       </c>
@@ -5402,12 +5473,12 @@
       <c r="K5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" ht="33.0" customHeight="1">
+    <row r="6" spans="1:13" ht="33" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>117</v>
       </c>
@@ -5430,7 +5501,7 @@
         <v>31</v>
       </c>
       <c r="H6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>121</v>
@@ -5441,12 +5512,12 @@
       <c r="K6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" ht="33.0" customHeight="1">
+    <row r="7" spans="1:13" ht="33" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>123</v>
       </c>
@@ -5468,7 +5539,7 @@
       <c r="G7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
         <v>127</v>
       </c>
@@ -5478,12 +5549,12 @@
       <c r="K7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" ht="33.0" customHeight="1">
+    <row r="8" spans="1:13" ht="33" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>129</v>
       </c>
@@ -5505,7 +5576,7 @@
       <c r="G8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
         <v>133</v>
       </c>
@@ -5515,12 +5586,12 @@
       <c r="K8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="9" ht="33.0" customHeight="1">
+    <row r="9" spans="1:13" ht="33" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>135</v>
       </c>
@@ -5542,7 +5613,7 @@
       <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
         <v>139</v>
       </c>
@@ -5552,12 +5623,12 @@
       <c r="K9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" ht="33.0" customHeight="1">
+    <row r="10" spans="1:13" ht="33" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>141</v>
       </c>
@@ -5579,7 +5650,7 @@
       <c r="G10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
         <v>145</v>
       </c>
@@ -5589,12 +5660,12 @@
       <c r="K10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="11" ht="33.0" customHeight="1">
+    <row r="11" spans="1:13" ht="33" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>147</v>
       </c>
@@ -5616,8 +5687,8 @@
       <c r="G11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="7" t="s">
         <v>151</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -5626,12 +5697,12 @@
       <c r="K11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" ht="33.0" customHeight="1">
+    <row r="12" spans="1:13" ht="33" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>153</v>
       </c>
@@ -5653,7 +5724,7 @@
       <c r="G12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
         <v>157</v>
       </c>
@@ -5663,12 +5734,12 @@
       <c r="K12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="11"/>
+      <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="13" ht="33.0" customHeight="1">
+    <row r="13" spans="1:13" ht="33" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>159</v>
       </c>
@@ -5684,13 +5755,13 @@
       <c r="E13" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="8" t="s">
         <v>162</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
         <v>163</v>
       </c>
@@ -5700,12 +5771,12 @@
       <c r="K13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="11"/>
+      <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="14" ht="33.0" customHeight="1">
+    <row r="14" spans="1:13" ht="33" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>165</v>
       </c>
@@ -5727,7 +5798,7 @@
       <c r="G14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="12"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
         <v>169</v>
       </c>
@@ -5737,12 +5808,12 @@
       <c r="K14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="11"/>
+      <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" ht="33.0" customHeight="1">
+    <row r="15" spans="1:13" ht="33" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>171</v>
       </c>
@@ -5764,7 +5835,7 @@
       <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="12"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
         <v>175</v>
       </c>
@@ -5774,12 +5845,12 @@
       <c r="K15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="11"/>
+      <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="16" ht="33.0" customHeight="1">
+    <row r="16" spans="1:13" ht="33" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>177</v>
       </c>
@@ -5801,8 +5872,8 @@
       <c r="G16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="14" t="s">
+      <c r="H16" s="3"/>
+      <c r="I16" s="8" t="s">
         <v>181</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -5811,12 +5882,12 @@
       <c r="K16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="17" ht="33.0" customHeight="1">
+    <row r="17" spans="1:26" ht="33" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>183</v>
       </c>
@@ -5838,7 +5909,7 @@
       <c r="G17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="12"/>
+      <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
         <v>187</v>
       </c>
@@ -5848,162 +5919,162 @@
       <c r="K17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" ht="33.0" customHeight="1">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:26" ht="33" customHeight="1">
+      <c r="A18" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="15" t="s">
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="10" t="s">
+      <c r="J18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="18"/>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
-      <c r="A19" s="15" t="s">
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+    </row>
+    <row r="19" spans="1:26" ht="33" customHeight="1">
+      <c r="A19" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="19" t="s">
+      <c r="H19" s="9"/>
+      <c r="I19" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="10" t="s">
+      <c r="J19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-    </row>
-    <row r="20" ht="33.0" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+    </row>
+    <row r="20" spans="1:26" ht="33" customHeight="1">
+      <c r="A20" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="15" t="s">
+      <c r="H20" s="9"/>
+      <c r="I20" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="J20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="17"/>
-      <c r="M20" s="10" t="s">
+      <c r="J20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-    </row>
-    <row r="21" ht="33.0" customHeight="1">
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+    </row>
+    <row r="21" spans="1:26" ht="33" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>207</v>
       </c>
@@ -6025,7 +6096,7 @@
       <c r="G21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="12"/>
+      <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
         <v>211</v>
       </c>
@@ -6035,22 +6106,22 @@
       <c r="K21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L21" s="11"/>
+      <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="22" ht="33.0" customHeight="1">
+    <row r="22" spans="1:26" ht="33" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -6062,7 +6133,7 @@
       <c r="G22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="12"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
         <v>217</v>
       </c>
@@ -6072,12 +6143,12 @@
       <c r="K22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L22" s="11"/>
+      <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="23" ht="33.0" customHeight="1">
+    <row r="23" spans="1:26" ht="33" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>219</v>
       </c>
@@ -6099,7 +6170,7 @@
       <c r="G23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="12"/>
+      <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
         <v>223</v>
       </c>
@@ -6109,12 +6180,12 @@
       <c r="K23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L23" s="11"/>
+      <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="24" ht="33.0" customHeight="1">
+    <row r="24" spans="1:26" ht="33" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>225</v>
       </c>
@@ -6136,7 +6207,7 @@
       <c r="G24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="12"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
         <v>229</v>
       </c>
@@ -6146,62 +6217,62 @@
       <c r="K24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L24" s="11"/>
+      <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="25" ht="33.0" customHeight="1">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:26" ht="33" customHeight="1">
+      <c r="A25" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="15" t="s">
+      <c r="H25" s="9"/>
+      <c r="I25" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="17"/>
-      <c r="M25" s="10" t="s">
+      <c r="J25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="18"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
-    </row>
-    <row r="26" ht="33.0" customHeight="1">
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+    </row>
+    <row r="26" spans="1:26" ht="33" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>237</v>
       </c>
@@ -6223,7 +6294,7 @@
       <c r="G26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="12"/>
+      <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
         <v>241</v>
       </c>
@@ -6233,12 +6304,12 @@
       <c r="K26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L26" s="11"/>
+      <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="27" ht="33.0" customHeight="1">
+    <row r="27" spans="1:26" ht="33" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>243</v>
       </c>
@@ -6260,7 +6331,7 @@
       <c r="G27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="12"/>
+      <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
         <v>247</v>
       </c>
@@ -6270,12 +6341,12 @@
       <c r="K27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="11"/>
+      <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" ht="33.0" customHeight="1">
+    <row r="28" spans="1:26" ht="33" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>249</v>
       </c>
@@ -6297,7 +6368,7 @@
       <c r="G28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="12"/>
+      <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
         <v>253</v>
       </c>
@@ -6307,212 +6378,212 @@
       <c r="K28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L28" s="11"/>
+      <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="29" ht="33.0" customHeight="1">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:26" ht="33" customHeight="1">
+      <c r="A29" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="15" t="s">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="J29" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="17"/>
-      <c r="M29" s="10" t="s">
+      <c r="J29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="18"/>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+    </row>
+    <row r="30" spans="1:26" ht="33" customHeight="1">
+      <c r="A30" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="15" t="s">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="J30" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="17"/>
-      <c r="M30" s="10" t="s">
+      <c r="J30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="15" t="s">
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+    </row>
+    <row r="31" spans="1:26" ht="33" customHeight="1">
+      <c r="A31" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="15" t="s">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="J31" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" s="17"/>
-      <c r="M31" s="10" t="s">
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-    </row>
-    <row r="32" ht="33.0" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+    </row>
+    <row r="32" spans="1:26" ht="33" customHeight="1">
+      <c r="A32" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="15" t="s">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="J32" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L32" s="17"/>
-      <c r="M32" s="10" t="s">
+      <c r="J32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-    </row>
-    <row r="33" ht="33.0" customHeight="1">
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+    </row>
+    <row r="33" spans="1:26" ht="33" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>279</v>
       </c>
@@ -6534,7 +6605,7 @@
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H33" s="12"/>
+      <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
         <v>283</v>
       </c>
@@ -6544,19 +6615,19 @@
       <c r="K33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L33" s="11"/>
+      <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="34" ht="33.0" customHeight="1">
-      <c r="A34" s="22" t="s">
+    <row r="34" spans="1:26" ht="33" customHeight="1">
+      <c r="A34" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="12" t="s">
         <v>286</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -6565,13 +6636,13 @@
       <c r="E34" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="7" t="s">
         <v>288</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="12"/>
+      <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
         <v>289</v>
       </c>
@@ -6581,19 +6652,19 @@
       <c r="K34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L34" s="11"/>
+      <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="35" ht="33.0" customHeight="1">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:26" ht="33" customHeight="1">
+      <c r="A35" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -6608,7 +6679,7 @@
       <c r="G35" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="12"/>
+      <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
         <v>295</v>
       </c>
@@ -6618,12 +6689,12 @@
       <c r="K35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L35" s="11"/>
+      <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="36" ht="52.5" customHeight="1">
+    <row r="36" spans="1:26" ht="52.5" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>297</v>
       </c>
@@ -6645,8 +6716,8 @@
       <c r="G36" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="23" t="s">
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
         <v>301</v>
       </c>
       <c r="J36" s="3" t="s">
@@ -6655,12 +6726,12 @@
       <c r="K36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L36" s="11"/>
+      <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="37" ht="43.5" customHeight="1">
+    <row r="37" spans="1:26" ht="43.5" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>303</v>
       </c>
@@ -6682,7 +6753,7 @@
       <c r="G37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="12"/>
+      <c r="H37" s="3"/>
       <c r="I37" s="3" t="s">
         <v>307</v>
       </c>
@@ -6692,12 +6763,12 @@
       <c r="K37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L37" s="11"/>
+      <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="38" ht="33.0" customHeight="1">
+    <row r="38" spans="1:26" ht="33" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>309</v>
       </c>
@@ -6719,7 +6790,7 @@
       <c r="G38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H38" s="12"/>
+      <c r="H38" s="3"/>
       <c r="I38" s="3" t="s">
         <v>313</v>
       </c>
@@ -6729,12 +6800,12 @@
       <c r="K38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L38" s="11"/>
+      <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="39" ht="33.0" customHeight="1">
+    <row r="39" spans="1:26" ht="33" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>315</v>
       </c>
@@ -6756,7 +6827,7 @@
       <c r="G39" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="12"/>
+      <c r="H39" s="3"/>
       <c r="I39" s="3" t="s">
         <v>319</v>
       </c>
@@ -6766,12 +6837,12 @@
       <c r="K39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="11"/>
+      <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="40" ht="33.0" customHeight="1">
+    <row r="40" spans="1:26" ht="33" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>321</v>
       </c>
@@ -6793,7 +6864,7 @@
       <c r="G40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="12"/>
+      <c r="H40" s="3"/>
       <c r="I40" s="3" t="s">
         <v>325</v>
       </c>
@@ -6803,12 +6874,12 @@
       <c r="K40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="11"/>
+      <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="41" ht="33.0" customHeight="1">
+    <row r="41" spans="1:26" ht="33" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>327</v>
       </c>
@@ -6830,7 +6901,7 @@
       <c r="G41" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="12"/>
+      <c r="H41" s="3"/>
       <c r="I41" s="3" t="s">
         <v>331</v>
       </c>
@@ -6840,12 +6911,12 @@
       <c r="K41" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L41" s="11"/>
+      <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="42" ht="33.0" customHeight="1">
+    <row r="42" spans="1:26" ht="33" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>333</v>
       </c>
@@ -6867,7 +6938,7 @@
       <c r="G42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="12"/>
+      <c r="H42" s="3"/>
       <c r="I42" s="3" t="s">
         <v>337</v>
       </c>
@@ -6877,12 +6948,12 @@
       <c r="K42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L42" s="11"/>
+      <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="43" ht="33.0" customHeight="1">
+    <row r="43" spans="1:26" ht="33" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>339</v>
       </c>
@@ -6904,7 +6975,7 @@
       <c r="G43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="12"/>
+      <c r="H43" s="3"/>
       <c r="I43" s="3" t="s">
         <v>343</v>
       </c>
@@ -6914,12 +6985,12 @@
       <c r="K43" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L43" s="11"/>
+      <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="44" ht="33.0" customHeight="1">
+    <row r="44" spans="1:26" ht="33" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>345</v>
       </c>
@@ -6941,7 +7012,7 @@
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="12"/>
+      <c r="H44" s="3"/>
       <c r="I44" s="3" t="s">
         <v>349</v>
       </c>
@@ -6951,12 +7022,12 @@
       <c r="K44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L44" s="11"/>
+      <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="45" ht="33.0" customHeight="1">
+    <row r="45" spans="1:26" ht="33" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>351</v>
       </c>
@@ -6978,7 +7049,7 @@
       <c r="G45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="12"/>
+      <c r="H45" s="3"/>
       <c r="I45" s="3" t="s">
         <v>355</v>
       </c>
@@ -6988,12 +7059,12 @@
       <c r="K45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="11"/>
+      <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="46" ht="33.0" customHeight="1">
+    <row r="46" spans="1:26" ht="33" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>357</v>
       </c>
@@ -7015,7 +7086,7 @@
       <c r="G46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="12"/>
+      <c r="H46" s="3"/>
       <c r="I46" s="3" t="s">
         <v>361</v>
       </c>
@@ -7025,62 +7096,62 @@
       <c r="K46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L46" s="11"/>
+      <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="47" ht="33.0" customHeight="1">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:26" ht="33" customHeight="1">
+      <c r="A47" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="16"/>
-      <c r="I47" s="15" t="s">
+      <c r="H47" s="9"/>
+      <c r="I47" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="J47" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L47" s="17"/>
-      <c r="M47" s="10" t="s">
+      <c r="J47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-    </row>
-    <row r="48" ht="33.0" customHeight="1">
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
+      <c r="X47" s="10"/>
+      <c r="Y47" s="10"/>
+      <c r="Z47" s="10"/>
+    </row>
+    <row r="48" spans="1:26" ht="33" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>369</v>
       </c>
@@ -7102,7 +7173,7 @@
       <c r="G48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="12"/>
+      <c r="H48" s="3"/>
       <c r="I48" s="3" t="s">
         <v>373</v>
       </c>
@@ -7112,12 +7183,12 @@
       <c r="K48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L48" s="11"/>
+      <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="49" ht="33.0" customHeight="1">
+    <row r="49" spans="1:13" ht="33" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>375</v>
       </c>
@@ -7139,7 +7210,7 @@
       <c r="G49" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="12"/>
+      <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>379</v>
       </c>
@@ -7149,12 +7220,12 @@
       <c r="K49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L49" s="11"/>
+      <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="50" ht="33.0" customHeight="1">
+    <row r="50" spans="1:13" ht="33" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>381</v>
       </c>
@@ -7176,7 +7247,7 @@
       <c r="G50" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H50" s="12"/>
+      <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
         <v>385</v>
       </c>
@@ -7186,12 +7257,12 @@
       <c r="K50" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L50" s="11"/>
+      <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="51" ht="33.0" customHeight="1">
+    <row r="51" spans="1:13" ht="33" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>387</v>
       </c>
@@ -7213,7 +7284,7 @@
       <c r="G51" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H51" s="12"/>
+      <c r="H51" s="3"/>
       <c r="I51" s="3" t="s">
         <v>391</v>
       </c>
@@ -7223,12 +7294,12 @@
       <c r="K51" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="11"/>
+      <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="52" ht="30.0" customHeight="1">
+    <row r="52" spans="1:13" ht="30" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>393</v>
       </c>
@@ -7250,7 +7321,7 @@
       <c r="G52" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H52" s="12"/>
+      <c r="H52" s="3"/>
       <c r="I52" s="3" t="s">
         <v>397</v>
       </c>
@@ -7260,12 +7331,12 @@
       <c r="K52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L52" s="11"/>
+      <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="53" ht="33.0" customHeight="1">
+    <row r="53" spans="1:13" ht="33" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>399</v>
       </c>
@@ -7287,7 +7358,7 @@
       <c r="G53" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="12"/>
+      <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
         <v>403</v>
       </c>
@@ -7297,12 +7368,12 @@
       <c r="K53" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L53" s="11"/>
+      <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="54" ht="33.0" customHeight="1">
+    <row r="54" spans="1:13" ht="33" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>405</v>
       </c>
@@ -7324,7 +7395,7 @@
       <c r="G54" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="12"/>
+      <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
         <v>409</v>
       </c>
@@ -7334,12 +7405,12 @@
       <c r="K54" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L54" s="11"/>
+      <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="55" ht="33.0" customHeight="1">
+    <row r="55" spans="1:13" ht="33" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>411</v>
       </c>
@@ -7361,7 +7432,7 @@
       <c r="G55" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H55" s="12"/>
+      <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
         <v>415</v>
       </c>
@@ -7371,12 +7442,12 @@
       <c r="K55" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="11"/>
+      <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="56" ht="33.0" customHeight="1">
+    <row r="56" spans="1:13" ht="33" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>417</v>
       </c>
@@ -7398,7 +7469,7 @@
       <c r="G56" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="12"/>
+      <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
         <v>421</v>
       </c>
@@ -7408,12 +7479,12 @@
       <c r="K56" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L56" s="11"/>
+      <c r="L56" s="4"/>
       <c r="M56" s="4" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="57" ht="33.0" customHeight="1">
+    <row r="57" spans="1:13" ht="33" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>423</v>
       </c>
@@ -7435,7 +7506,7 @@
       <c r="G57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H57" s="12"/>
+      <c r="H57" s="3"/>
       <c r="I57" s="3" t="s">
         <v>427</v>
       </c>
@@ -7445,12 +7516,12 @@
       <c r="K57" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L57" s="11"/>
+      <c r="L57" s="4"/>
       <c r="M57" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="58" ht="33.0" customHeight="1">
+    <row r="58" spans="1:13" ht="33" customHeight="1">
       <c r="A58" s="3" t="s">
         <v>429</v>
       </c>
@@ -7472,7 +7543,7 @@
       <c r="G58" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="12"/>
+      <c r="H58" s="3"/>
       <c r="I58" s="3" t="s">
         <v>433</v>
       </c>
@@ -7482,12 +7553,12 @@
       <c r="K58" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L58" s="11"/>
+      <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="59" ht="33.0" customHeight="1">
+    <row r="59" spans="1:13" ht="33" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>435</v>
       </c>
@@ -7509,7 +7580,7 @@
       <c r="G59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="12"/>
+      <c r="H59" s="3"/>
       <c r="I59" s="3" t="s">
         <v>439</v>
       </c>
@@ -7519,12 +7590,12 @@
       <c r="K59" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L59" s="11"/>
+      <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="60" ht="33.0" customHeight="1">
+    <row r="60" spans="1:13" ht="33" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>441</v>
       </c>
@@ -7546,7 +7617,7 @@
       <c r="G60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H60" s="12"/>
+      <c r="H60" s="3"/>
       <c r="I60" s="3" t="s">
         <v>445</v>
       </c>
@@ -7556,12 +7627,12 @@
       <c r="K60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L60" s="11"/>
+      <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="61" ht="33.0" customHeight="1">
+    <row r="61" spans="1:13" ht="33" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>447</v>
       </c>
@@ -7583,7 +7654,7 @@
       <c r="G61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="12"/>
+      <c r="H61" s="3"/>
       <c r="I61" s="3" t="s">
         <v>451</v>
       </c>
@@ -7593,12 +7664,12 @@
       <c r="K61" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L61" s="11"/>
+      <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="62" ht="33.0" customHeight="1">
+    <row r="62" spans="1:13" ht="33" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>453</v>
       </c>
@@ -7620,7 +7691,7 @@
       <c r="G62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H62" s="12"/>
+      <c r="H62" s="3"/>
       <c r="I62" s="3" t="s">
         <v>457</v>
       </c>
@@ -7630,12 +7701,12 @@
       <c r="K62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L62" s="11"/>
+      <c r="L62" s="4"/>
       <c r="M62" s="4" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="63" ht="33.0" customHeight="1">
+    <row r="63" spans="1:13" ht="33" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>459</v>
       </c>
@@ -7657,7 +7728,7 @@
       <c r="G63" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H63" s="12"/>
+      <c r="H63" s="3"/>
       <c r="I63" s="3" t="s">
         <v>463</v>
       </c>
@@ -7667,12 +7738,12 @@
       <c r="K63" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L63" s="11"/>
+      <c r="L63" s="4"/>
       <c r="M63" s="4" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="64" ht="33.0" customHeight="1">
+    <row r="64" spans="1:13" ht="33" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>465</v>
       </c>
@@ -7694,7 +7765,7 @@
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H64" s="12"/>
+      <c r="H64" s="3"/>
       <c r="I64" s="3" t="s">
         <v>469</v>
       </c>
@@ -7704,12 +7775,12 @@
       <c r="K64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L64" s="11"/>
+      <c r="L64" s="4"/>
       <c r="M64" s="4" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="65" ht="33.0" customHeight="1">
+    <row r="65" spans="1:13" ht="33" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>471</v>
       </c>
@@ -7731,7 +7802,7 @@
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="12"/>
+      <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
         <v>475</v>
       </c>
@@ -7741,12 +7812,12 @@
       <c r="K65" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L65" s="11"/>
+      <c r="L65" s="4"/>
       <c r="M65" s="4" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="66" ht="33.0" customHeight="1">
+    <row r="66" spans="1:13" ht="33" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>477</v>
       </c>
@@ -7768,7 +7839,7 @@
       <c r="G66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H66" s="12"/>
+      <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
         <v>481</v>
       </c>
@@ -7778,12 +7849,12 @@
       <c r="K66" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L66" s="11"/>
+      <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="67" ht="33.0" customHeight="1">
+    <row r="67" spans="1:13" ht="33" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>483</v>
       </c>
@@ -7805,7 +7876,7 @@
       <c r="G67" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H67" s="12"/>
+      <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
         <v>487</v>
       </c>
@@ -7815,12 +7886,12 @@
       <c r="K67" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L67" s="11"/>
+      <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="68" ht="33.0" customHeight="1">
+    <row r="68" spans="1:13" ht="33" customHeight="1">
       <c r="A68" s="3" t="s">
         <v>489</v>
       </c>
@@ -7842,7 +7913,7 @@
       <c r="G68" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H68" s="12"/>
+      <c r="H68" s="3"/>
       <c r="I68" s="3" t="s">
         <v>493</v>
       </c>
@@ -7852,12 +7923,12 @@
       <c r="K68" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L68" s="11"/>
+      <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="69" ht="33.0" customHeight="1">
+    <row r="69" spans="1:13" ht="33" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>495</v>
       </c>
@@ -7879,7 +7950,7 @@
       <c r="G69" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H69" s="12"/>
+      <c r="H69" s="3"/>
       <c r="I69" s="3" t="s">
         <v>499</v>
       </c>
@@ -7889,12 +7960,12 @@
       <c r="K69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L69" s="11"/>
+      <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="70" ht="33.0" customHeight="1">
+    <row r="70" spans="1:13" ht="33" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>501</v>
       </c>
@@ -7916,7 +7987,7 @@
       <c r="G70" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H70" s="12"/>
+      <c r="H70" s="3"/>
       <c r="I70" s="3" t="s">
         <v>505</v>
       </c>
@@ -7926,12 +7997,12 @@
       <c r="K70" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L70" s="11"/>
+      <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="71" ht="33.0" customHeight="1">
+    <row r="71" spans="1:13" ht="33" customHeight="1">
       <c r="A71" s="3" t="s">
         <v>507</v>
       </c>
@@ -7953,7 +8024,7 @@
       <c r="G71" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H71" s="12"/>
+      <c r="H71" s="3"/>
       <c r="I71" s="3" t="s">
         <v>511</v>
       </c>
@@ -7963,12 +8034,12 @@
       <c r="K71" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L71" s="11"/>
+      <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="72" ht="33.0" customHeight="1">
+    <row r="72" spans="1:13" ht="33" customHeight="1">
       <c r="A72" s="3" t="s">
         <v>513</v>
       </c>
@@ -7990,7 +8061,7 @@
       <c r="G72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H72" s="12"/>
+      <c r="H72" s="3"/>
       <c r="I72" s="3" t="s">
         <v>517</v>
       </c>
@@ -8000,12 +8071,12 @@
       <c r="K72" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L72" s="11"/>
+      <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="73" ht="33.0" customHeight="1">
+    <row r="73" spans="1:13" ht="33" customHeight="1">
       <c r="A73" s="3" t="s">
         <v>519</v>
       </c>
@@ -8027,7 +8098,7 @@
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="12"/>
+      <c r="H73" s="3"/>
       <c r="I73" s="3" t="s">
         <v>523</v>
       </c>
@@ -8037,12 +8108,12 @@
       <c r="K73" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L73" s="11"/>
+      <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="74" ht="33.0" customHeight="1">
+    <row r="74" spans="1:13" ht="33" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>525</v>
       </c>
@@ -8064,7 +8135,7 @@
       <c r="G74" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H74" s="12"/>
+      <c r="H74" s="3"/>
       <c r="I74" s="3" t="s">
         <v>529</v>
       </c>
@@ -8074,12 +8145,12 @@
       <c r="K74" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L74" s="11"/>
+      <c r="L74" s="4"/>
       <c r="M74" s="4" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="75" ht="33.0" customHeight="1">
+    <row r="75" spans="1:13" ht="33" customHeight="1">
       <c r="A75" s="3" t="s">
         <v>531</v>
       </c>
@@ -8101,7 +8172,7 @@
       <c r="G75" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H75" s="12"/>
+      <c r="H75" s="3"/>
       <c r="I75" s="3" t="s">
         <v>535</v>
       </c>
@@ -8111,12 +8182,12 @@
       <c r="K75" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L75" s="11"/>
+      <c r="L75" s="4"/>
       <c r="M75" s="4" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="76" ht="33.0" customHeight="1">
+    <row r="76" spans="1:13" ht="33" customHeight="1">
       <c r="A76" s="3" t="s">
         <v>537</v>
       </c>
@@ -8138,7 +8209,7 @@
       <c r="G76" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H76" s="12"/>
+      <c r="H76" s="3"/>
       <c r="I76" s="3" t="s">
         <v>541</v>
       </c>
@@ -8148,12 +8219,12 @@
       <c r="K76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L76" s="11"/>
+      <c r="L76" s="4"/>
       <c r="M76" s="4" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="77" ht="33.0" customHeight="1">
+    <row r="77" spans="1:13" ht="33" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>543</v>
       </c>
@@ -8175,7 +8246,7 @@
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H77" s="12"/>
+      <c r="H77" s="3"/>
       <c r="I77" s="3" t="s">
         <v>547</v>
       </c>
@@ -8185,12 +8256,12 @@
       <c r="K77" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L77" s="11"/>
+      <c r="L77" s="4"/>
       <c r="M77" s="4" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="78" ht="33.0" customHeight="1">
+    <row r="78" spans="1:13" ht="33" customHeight="1">
       <c r="A78" s="3" t="s">
         <v>549</v>
       </c>
@@ -8212,7 +8283,7 @@
       <c r="G78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H78" s="12"/>
+      <c r="H78" s="3"/>
       <c r="I78" s="3" t="s">
         <v>553</v>
       </c>
@@ -8222,12 +8293,12 @@
       <c r="K78" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L78" s="11"/>
+      <c r="L78" s="4"/>
       <c r="M78" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="79" ht="33.0" customHeight="1">
+    <row r="79" spans="1:13" ht="33" customHeight="1">
       <c r="A79" s="3" t="s">
         <v>555</v>
       </c>
@@ -8249,7 +8320,7 @@
       <c r="G79" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H79" s="12"/>
+      <c r="H79" s="3"/>
       <c r="I79" s="3" t="s">
         <v>559</v>
       </c>
@@ -8259,12 +8330,12 @@
       <c r="K79" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L79" s="11"/>
+      <c r="L79" s="4"/>
       <c r="M79" s="4" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="80" ht="33.0" customHeight="1">
+    <row r="80" spans="1:13" ht="33" customHeight="1">
       <c r="A80" s="3" t="s">
         <v>561</v>
       </c>
@@ -8286,7 +8357,7 @@
       <c r="G80" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H80" s="12"/>
+      <c r="H80" s="3"/>
       <c r="I80" s="3" t="s">
         <v>565</v>
       </c>
@@ -8296,12 +8367,12 @@
       <c r="K80" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L80" s="11"/>
+      <c r="L80" s="4"/>
       <c r="M80" s="4" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="81" ht="33.0" customHeight="1">
+    <row r="81" spans="1:13" ht="33" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>567</v>
       </c>
@@ -8323,7 +8394,7 @@
       <c r="G81" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H81" s="12"/>
+      <c r="H81" s="3"/>
       <c r="I81" s="3" t="s">
         <v>571</v>
       </c>
@@ -8333,12 +8404,12 @@
       <c r="K81" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L81" s="11"/>
+      <c r="L81" s="4"/>
       <c r="M81" s="4" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="82" ht="33.0" customHeight="1">
+    <row r="82" spans="1:13" ht="33" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>573</v>
       </c>
@@ -8360,7 +8431,7 @@
       <c r="G82" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H82" s="12"/>
+      <c r="H82" s="3"/>
       <c r="I82" s="3" t="s">
         <v>577</v>
       </c>
@@ -8370,12 +8441,12 @@
       <c r="K82" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L82" s="11"/>
+      <c r="L82" s="4"/>
       <c r="M82" s="4" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="83" ht="33.0" customHeight="1">
+    <row r="83" spans="1:13" ht="33" customHeight="1">
       <c r="A83" s="3" t="s">
         <v>579</v>
       </c>
@@ -8397,7 +8468,7 @@
       <c r="G83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H83" s="12"/>
+      <c r="H83" s="3"/>
       <c r="I83" s="3" t="s">
         <v>583</v>
       </c>
@@ -8407,12 +8478,12 @@
       <c r="K83" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L83" s="11"/>
+      <c r="L83" s="4"/>
       <c r="M83" s="4" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="84" ht="33.0" customHeight="1">
+    <row r="84" spans="1:13" ht="33" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>585</v>
       </c>
@@ -8434,7 +8505,7 @@
       <c r="G84" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H84" s="12"/>
+      <c r="H84" s="3"/>
       <c r="I84" s="3" t="s">
         <v>589</v>
       </c>
@@ -8444,12 +8515,12 @@
       <c r="K84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L84" s="11"/>
+      <c r="L84" s="4"/>
       <c r="M84" s="4" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="85" ht="33.0" customHeight="1">
+    <row r="85" spans="1:13" ht="33" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>591</v>
       </c>
@@ -8471,7 +8542,7 @@
       <c r="G85" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H85" s="12"/>
+      <c r="H85" s="3"/>
       <c r="I85" s="3" t="s">
         <v>595</v>
       </c>
@@ -8481,12 +8552,12 @@
       <c r="K85" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L85" s="11"/>
+      <c r="L85" s="4"/>
       <c r="M85" s="4" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="86" ht="33.0" customHeight="1">
+    <row r="86" spans="1:13" ht="33" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>597</v>
       </c>
@@ -8508,7 +8579,7 @@
       <c r="G86" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H86" s="12"/>
+      <c r="H86" s="3"/>
       <c r="I86" s="3" t="s">
         <v>601</v>
       </c>
@@ -8518,12 +8589,12 @@
       <c r="K86" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L86" s="11"/>
+      <c r="L86" s="4"/>
       <c r="M86" s="4" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="87" ht="33.0" customHeight="1">
+    <row r="87" spans="1:13" ht="33" customHeight="1">
       <c r="A87" s="3" t="s">
         <v>603</v>
       </c>
@@ -8545,7 +8616,7 @@
       <c r="G87" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H87" s="12"/>
+      <c r="H87" s="3"/>
       <c r="I87" s="3" t="s">
         <v>608</v>
       </c>
@@ -8555,12 +8626,12 @@
       <c r="K87" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L87" s="11"/>
+      <c r="L87" s="4"/>
       <c r="M87" s="4" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="88" ht="33.0" customHeight="1">
+    <row r="88" spans="1:13" ht="33" customHeight="1">
       <c r="A88" s="3" t="s">
         <v>610</v>
       </c>
@@ -8582,7 +8653,7 @@
       <c r="G88" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H88" s="12"/>
+      <c r="H88" s="3"/>
       <c r="I88" s="3" t="s">
         <v>614</v>
       </c>
@@ -8592,12 +8663,12 @@
       <c r="K88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L88" s="11"/>
+      <c r="L88" s="4"/>
       <c r="M88" s="4" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="89" ht="33.0" customHeight="1">
+    <row r="89" spans="1:13" ht="33" customHeight="1">
       <c r="A89" s="3" t="s">
         <v>616</v>
       </c>
@@ -8619,7 +8690,7 @@
       <c r="G89" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H89" s="12"/>
+      <c r="H89" s="3"/>
       <c r="I89" s="3" t="s">
         <v>620</v>
       </c>
@@ -8629,12 +8700,12 @@
       <c r="K89" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L89" s="11"/>
+      <c r="L89" s="4"/>
       <c r="M89" s="4" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="90" ht="33.0" customHeight="1">
+    <row r="90" spans="1:13" ht="33" customHeight="1">
       <c r="A90" s="3" t="s">
         <v>622</v>
       </c>
@@ -8656,7 +8727,7 @@
       <c r="G90" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H90" s="12"/>
+      <c r="H90" s="3"/>
       <c r="I90" s="3" t="s">
         <v>626</v>
       </c>
@@ -8666,12 +8737,12 @@
       <c r="K90" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L90" s="11"/>
+      <c r="L90" s="4"/>
       <c r="M90" s="4" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="91" ht="33.0" customHeight="1">
+    <row r="91" spans="1:13" ht="33" customHeight="1">
       <c r="A91" s="3" t="s">
         <v>628</v>
       </c>
@@ -8693,7 +8764,7 @@
       <c r="G91" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H91" s="12"/>
+      <c r="H91" s="3"/>
       <c r="I91" s="3" t="s">
         <v>632</v>
       </c>
@@ -8703,12 +8774,12 @@
       <c r="K91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L91" s="11"/>
+      <c r="L91" s="4"/>
       <c r="M91" s="4" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="92" ht="33.0" customHeight="1">
+    <row r="92" spans="1:13" ht="33" customHeight="1">
       <c r="A92" s="3" t="s">
         <v>634</v>
       </c>
@@ -8730,7 +8801,7 @@
       <c r="G92" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H92" s="12"/>
+      <c r="H92" s="3"/>
       <c r="I92" s="3" t="s">
         <v>638</v>
       </c>
@@ -8740,12 +8811,12 @@
       <c r="K92" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L92" s="11"/>
+      <c r="L92" s="4"/>
       <c r="M92" s="4" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="93" ht="33.0" customHeight="1">
+    <row r="93" spans="1:13" ht="33" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>640</v>
       </c>
@@ -8767,7 +8838,7 @@
       <c r="G93" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H93" s="12"/>
+      <c r="H93" s="3"/>
       <c r="I93" s="3" t="s">
         <v>644</v>
       </c>
@@ -8777,12 +8848,12 @@
       <c r="K93" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L93" s="11"/>
+      <c r="L93" s="4"/>
       <c r="M93" s="4" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="94" ht="33.0" customHeight="1">
+    <row r="94" spans="1:13" ht="33" customHeight="1">
       <c r="A94" s="3" t="s">
         <v>646</v>
       </c>
@@ -8804,7 +8875,7 @@
       <c r="G94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H94" s="12"/>
+      <c r="H94" s="3"/>
       <c r="I94" s="3" t="s">
         <v>650</v>
       </c>
@@ -8814,12 +8885,12 @@
       <c r="K94" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L94" s="11"/>
+      <c r="L94" s="4"/>
       <c r="M94" s="4" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="95" ht="33.0" customHeight="1">
+    <row r="95" spans="1:13" ht="33" customHeight="1">
       <c r="A95" s="3" t="s">
         <v>652</v>
       </c>
@@ -8841,7 +8912,7 @@
       <c r="G95" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H95" s="12"/>
+      <c r="H95" s="3"/>
       <c r="I95" s="3" t="s">
         <v>656</v>
       </c>
@@ -8851,12 +8922,12 @@
       <c r="K95" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L95" s="11"/>
+      <c r="L95" s="4"/>
       <c r="M95" s="4" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="96" ht="33.0" customHeight="1">
+    <row r="96" spans="1:13" ht="33" customHeight="1">
       <c r="A96" s="3" t="s">
         <v>658</v>
       </c>
@@ -8878,7 +8949,7 @@
       <c r="G96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H96" s="12"/>
+      <c r="H96" s="3"/>
       <c r="I96" s="3" t="s">
         <v>662</v>
       </c>
@@ -8888,12 +8959,12 @@
       <c r="K96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="11"/>
+      <c r="L96" s="4"/>
       <c r="M96" s="4" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="97" ht="33.0" customHeight="1">
+    <row r="97" spans="1:13" ht="33" customHeight="1">
       <c r="A97" s="3" t="s">
         <v>664</v>
       </c>
@@ -8915,7 +8986,7 @@
       <c r="G97" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H97" s="12"/>
+      <c r="H97" s="3"/>
       <c r="I97" s="3" t="s">
         <v>668</v>
       </c>
@@ -8925,12 +8996,12 @@
       <c r="K97" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L97" s="11"/>
+      <c r="L97" s="4"/>
       <c r="M97" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="98" ht="33.0" customHeight="1">
+    <row r="98" spans="1:13" ht="33" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>670</v>
       </c>
@@ -8952,7 +9023,7 @@
       <c r="G98" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H98" s="12"/>
+      <c r="H98" s="3"/>
       <c r="I98" s="3" t="s">
         <v>674</v>
       </c>
@@ -8962,12 +9033,12 @@
       <c r="K98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L98" s="11"/>
+      <c r="L98" s="4"/>
       <c r="M98" s="4" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="99" ht="33.0" customHeight="1">
+    <row r="99" spans="1:13" ht="33" customHeight="1">
       <c r="A99" s="3" t="s">
         <v>676</v>
       </c>
@@ -8989,7 +9060,7 @@
       <c r="G99" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H99" s="12"/>
+      <c r="H99" s="3"/>
       <c r="I99" s="3" t="s">
         <v>680</v>
       </c>
@@ -8999,12 +9070,12 @@
       <c r="K99" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L99" s="11"/>
+      <c r="L99" s="4"/>
       <c r="M99" s="4" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="100" ht="33.0" customHeight="1">
+    <row r="100" spans="1:13" ht="33" customHeight="1">
       <c r="A100" s="3" t="s">
         <v>682</v>
       </c>
@@ -9026,7 +9097,7 @@
       <c r="G100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="12"/>
+      <c r="H100" s="3"/>
       <c r="I100" s="3" t="s">
         <v>685</v>
       </c>
@@ -9036,12 +9107,12 @@
       <c r="K100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L100" s="11"/>
+      <c r="L100" s="4"/>
       <c r="M100" s="4" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="101" ht="33.0" customHeight="1">
+    <row r="101" spans="1:13" ht="33" customHeight="1">
       <c r="A101" s="3" t="s">
         <v>687</v>
       </c>
@@ -9063,7 +9134,7 @@
       <c r="G101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H101" s="12"/>
+      <c r="H101" s="3"/>
       <c r="I101" s="3" t="s">
         <v>691</v>
       </c>
@@ -9073,12 +9144,12 @@
       <c r="K101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L101" s="11"/>
+      <c r="L101" s="4"/>
       <c r="M101" s="4" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="102" ht="33.0" customHeight="1">
+    <row r="102" spans="1:13" ht="33" customHeight="1">
       <c r="A102" s="3" t="s">
         <v>693</v>
       </c>
@@ -9100,7 +9171,7 @@
       <c r="G102" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H102" s="12"/>
+      <c r="H102" s="3"/>
       <c r="I102" s="3" t="s">
         <v>697</v>
       </c>
@@ -9110,12 +9181,12 @@
       <c r="K102" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L102" s="11"/>
+      <c r="L102" s="4"/>
       <c r="M102" s="4" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="103" ht="33.0" customHeight="1">
+    <row r="103" spans="1:13" ht="33" customHeight="1">
       <c r="A103" s="3" t="s">
         <v>699</v>
       </c>
@@ -9137,7 +9208,7 @@
       <c r="G103" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H103" s="12"/>
+      <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
         <v>703</v>
       </c>
@@ -9147,12 +9218,12 @@
       <c r="K103" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L103" s="11"/>
+      <c r="L103" s="4"/>
       <c r="M103" s="4" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="104" ht="33.0" customHeight="1">
+    <row r="104" spans="1:13" ht="33" customHeight="1">
       <c r="A104" s="3" t="s">
         <v>705</v>
       </c>
@@ -9174,7 +9245,7 @@
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H104" s="12"/>
+      <c r="H104" s="3"/>
       <c r="I104" s="3" t="s">
         <v>709</v>
       </c>
@@ -9184,12 +9255,12 @@
       <c r="K104" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L104" s="11"/>
+      <c r="L104" s="4"/>
       <c r="M104" s="4" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="105" ht="33.0" customHeight="1">
+    <row r="105" spans="1:13" ht="33" customHeight="1">
       <c r="A105" s="3" t="s">
         <v>711</v>
       </c>
@@ -9211,7 +9282,7 @@
       <c r="G105" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H105" s="12"/>
+      <c r="H105" s="3"/>
       <c r="I105" s="3" t="s">
         <v>715</v>
       </c>
@@ -9221,1458 +9292,1458 @@
       <c r="K105" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L105" s="11"/>
+      <c r="L105" s="4"/>
       <c r="M105" s="4" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="106" ht="33.0" customHeight="1">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="12"/>
-      <c r="I106" s="12"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12"/>
-      <c r="L106" s="11"/>
-      <c r="M106" s="11"/>
-    </row>
-    <row r="107" ht="33.0" customHeight="1">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="12"/>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="11"/>
-      <c r="M107" s="11"/>
-    </row>
-    <row r="108" ht="33.0" customHeight="1">
-      <c r="A108" s="12"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="12"/>
-      <c r="H108" s="12"/>
-      <c r="I108" s="12"/>
-      <c r="J108" s="12"/>
-      <c r="K108" s="12"/>
-      <c r="L108" s="11"/>
-      <c r="M108" s="11"/>
-    </row>
-    <row r="109" ht="33.0" customHeight="1">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="12"/>
-      <c r="H109" s="12"/>
-      <c r="I109" s="12"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
-      <c r="L109" s="11"/>
-      <c r="M109" s="11"/>
-    </row>
-    <row r="110" ht="33.0" customHeight="1">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="12"/>
-      <c r="I110" s="12"/>
-      <c r="J110" s="12"/>
-      <c r="K110" s="12"/>
-      <c r="L110" s="11"/>
-      <c r="M110" s="11"/>
-    </row>
-    <row r="111" ht="33.0" customHeight="1">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="12"/>
-      <c r="H111" s="12"/>
-      <c r="I111" s="12"/>
-      <c r="J111" s="12"/>
-      <c r="K111" s="12"/>
-      <c r="L111" s="11"/>
-      <c r="M111" s="11"/>
-    </row>
-    <row r="112" ht="33.0" customHeight="1">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="12"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
-      <c r="L112" s="11"/>
-      <c r="M112" s="11"/>
-    </row>
-    <row r="113" ht="33.0" customHeight="1">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
-      <c r="G113" s="12"/>
-      <c r="H113" s="12"/>
-      <c r="I113" s="12"/>
-      <c r="J113" s="12"/>
-      <c r="K113" s="12"/>
-      <c r="L113" s="11"/>
-      <c r="M113" s="11"/>
-    </row>
-    <row r="114" ht="33.0" customHeight="1">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
-      <c r="G114" s="12"/>
-      <c r="H114" s="12"/>
-      <c r="I114" s="12"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="12"/>
-      <c r="L114" s="11"/>
-      <c r="M114" s="11"/>
-    </row>
-    <row r="115" ht="33.0" customHeight="1">
-      <c r="A115" s="12"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="12"/>
-      <c r="H115" s="12"/>
-      <c r="I115" s="12"/>
-      <c r="J115" s="12"/>
-      <c r="K115" s="12"/>
-      <c r="L115" s="11"/>
-      <c r="M115" s="11"/>
-    </row>
-    <row r="116" ht="33.0" customHeight="1">
-      <c r="A116" s="12"/>
-      <c r="B116" s="12"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="12"/>
-      <c r="H116" s="12"/>
-      <c r="I116" s="12"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="12"/>
-      <c r="L116" s="11"/>
-      <c r="M116" s="11"/>
-    </row>
-    <row r="117" ht="33.0" customHeight="1">
-      <c r="A117" s="12"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="11"/>
-      <c r="M117" s="11"/>
-    </row>
-    <row r="118" ht="33.0" customHeight="1">
-      <c r="A118" s="12"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="12"/>
-      <c r="H118" s="12"/>
-      <c r="I118" s="12"/>
-      <c r="J118" s="12"/>
-      <c r="K118" s="12"/>
-      <c r="L118" s="11"/>
-      <c r="M118" s="11"/>
-    </row>
-    <row r="119" ht="33.0" customHeight="1">
-      <c r="A119" s="12"/>
-      <c r="B119" s="12"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="11"/>
-      <c r="M119" s="11"/>
-    </row>
-    <row r="120" ht="33.0" customHeight="1">
-      <c r="A120" s="12"/>
-      <c r="B120" s="12"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="12"/>
-      <c r="H120" s="12"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="12"/>
-      <c r="K120" s="12"/>
-      <c r="L120" s="11"/>
-      <c r="M120" s="11"/>
-    </row>
-    <row r="121" ht="33.0" customHeight="1">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="11"/>
-      <c r="M121" s="11"/>
-    </row>
-    <row r="122" ht="33.0" customHeight="1">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
-      <c r="G122" s="12"/>
-      <c r="H122" s="12"/>
-      <c r="I122" s="12"/>
-      <c r="J122" s="12"/>
-      <c r="K122" s="12"/>
-      <c r="L122" s="11"/>
-      <c r="M122" s="11"/>
-    </row>
-    <row r="123" ht="33.0" customHeight="1">
-      <c r="A123" s="12"/>
-      <c r="B123" s="12"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="11"/>
-      <c r="M123" s="11"/>
-    </row>
-    <row r="124" ht="33.0" customHeight="1">
-      <c r="A124" s="12"/>
-      <c r="B124" s="12"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="12"/>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="12"/>
-      <c r="K124" s="12"/>
-      <c r="L124" s="11"/>
-      <c r="M124" s="11"/>
-    </row>
-    <row r="125" ht="33.0" customHeight="1">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="12"/>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="12"/>
-      <c r="K125" s="12"/>
-      <c r="L125" s="11"/>
-      <c r="M125" s="11"/>
-    </row>
-    <row r="126" ht="33.0" customHeight="1">
-      <c r="A126" s="12"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
-      <c r="G126" s="12"/>
-      <c r="H126" s="12"/>
-      <c r="I126" s="12"/>
-      <c r="J126" s="12"/>
-      <c r="K126" s="12"/>
-      <c r="L126" s="11"/>
-      <c r="M126" s="11"/>
-    </row>
-    <row r="127" ht="33.0" customHeight="1">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="12"/>
-      <c r="H127" s="12"/>
-      <c r="I127" s="12"/>
-      <c r="J127" s="12"/>
-      <c r="K127" s="12"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-    </row>
-    <row r="128" ht="33.0" customHeight="1">
-      <c r="A128" s="12"/>
-      <c r="B128" s="12"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="12"/>
-      <c r="H128" s="12"/>
-      <c r="I128" s="12"/>
-      <c r="J128" s="12"/>
-      <c r="K128" s="12"/>
-      <c r="L128" s="11"/>
-      <c r="M128" s="11"/>
-    </row>
-    <row r="129" ht="33.0" customHeight="1">
-      <c r="A129" s="12"/>
-      <c r="B129" s="12"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="12"/>
-      <c r="H129" s="12"/>
-      <c r="I129" s="12"/>
-      <c r="J129" s="12"/>
-      <c r="K129" s="12"/>
-      <c r="L129" s="11"/>
-      <c r="M129" s="11"/>
-    </row>
-    <row r="130" ht="33.0" customHeight="1">
-      <c r="A130" s="12"/>
-      <c r="B130" s="12"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="12"/>
-      <c r="H130" s="12"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="12"/>
-      <c r="K130" s="12"/>
-      <c r="L130" s="11"/>
-      <c r="M130" s="11"/>
-    </row>
-    <row r="131" ht="33.0" customHeight="1">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="12"/>
-      <c r="H131" s="12"/>
-      <c r="I131" s="12"/>
-      <c r="J131" s="12"/>
-      <c r="K131" s="12"/>
-      <c r="L131" s="11"/>
-      <c r="M131" s="11"/>
-    </row>
-    <row r="132" ht="33.0" customHeight="1">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="12"/>
-      <c r="H132" s="12"/>
-      <c r="I132" s="12"/>
-      <c r="J132" s="12"/>
-      <c r="K132" s="12"/>
-      <c r="L132" s="11"/>
-      <c r="M132" s="11"/>
-    </row>
-    <row r="133" ht="33.0" customHeight="1">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="12"/>
-      <c r="H133" s="12"/>
-      <c r="I133" s="12"/>
-      <c r="J133" s="12"/>
-      <c r="K133" s="12"/>
-      <c r="L133" s="11"/>
-      <c r="M133" s="11"/>
-    </row>
-    <row r="134" ht="33.0" customHeight="1">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
-      <c r="G134" s="12"/>
-      <c r="H134" s="12"/>
-      <c r="I134" s="12"/>
-      <c r="J134" s="12"/>
-      <c r="K134" s="12"/>
-      <c r="L134" s="11"/>
-      <c r="M134" s="11"/>
-    </row>
-    <row r="135" ht="33.0" customHeight="1">
-      <c r="A135" s="12"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
-      <c r="G135" s="12"/>
-      <c r="H135" s="12"/>
-      <c r="I135" s="12"/>
-      <c r="J135" s="12"/>
-      <c r="K135" s="12"/>
-      <c r="L135" s="11"/>
-      <c r="M135" s="11"/>
-    </row>
-    <row r="136" ht="33.0" customHeight="1">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="12"/>
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
-      <c r="L136" s="11"/>
-      <c r="M136" s="11"/>
-    </row>
-    <row r="137" ht="33.0" customHeight="1">
-      <c r="A137" s="12"/>
-      <c r="B137" s="12"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="12"/>
-      <c r="H137" s="12"/>
-      <c r="I137" s="12"/>
-      <c r="J137" s="12"/>
-      <c r="K137" s="12"/>
-      <c r="L137" s="11"/>
-      <c r="M137" s="11"/>
-    </row>
-    <row r="138" ht="33.0" customHeight="1">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="12"/>
-      <c r="H138" s="12"/>
-      <c r="I138" s="12"/>
-      <c r="J138" s="12"/>
-      <c r="K138" s="12"/>
-      <c r="L138" s="11"/>
-      <c r="M138" s="11"/>
-    </row>
-    <row r="139" ht="33.0" customHeight="1">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="12"/>
-      <c r="H139" s="12"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12"/>
-      <c r="K139" s="12"/>
-      <c r="L139" s="11"/>
-      <c r="M139" s="11"/>
-    </row>
-    <row r="140" ht="33.0" customHeight="1">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="12"/>
-      <c r="H140" s="12"/>
-      <c r="I140" s="12"/>
-      <c r="J140" s="12"/>
-      <c r="K140" s="12"/>
-      <c r="L140" s="11"/>
-      <c r="M140" s="11"/>
-    </row>
-    <row r="141" ht="33.0" customHeight="1">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="12"/>
-      <c r="H141" s="12"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="12"/>
-      <c r="K141" s="12"/>
-      <c r="L141" s="11"/>
-      <c r="M141" s="11"/>
-    </row>
-    <row r="142" ht="33.0" customHeight="1">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="12"/>
-      <c r="H142" s="12"/>
-      <c r="I142" s="12"/>
-      <c r="J142" s="12"/>
-      <c r="K142" s="12"/>
-      <c r="L142" s="11"/>
-      <c r="M142" s="11"/>
-    </row>
-    <row r="143" ht="33.0" customHeight="1">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="12"/>
-      <c r="H143" s="12"/>
-      <c r="I143" s="12"/>
-      <c r="J143" s="12"/>
-      <c r="K143" s="12"/>
-      <c r="L143" s="11"/>
-      <c r="M143" s="11"/>
-    </row>
-    <row r="144" ht="33.0" customHeight="1">
-      <c r="A144" s="12"/>
-      <c r="B144" s="12"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="12"/>
-      <c r="H144" s="12"/>
-      <c r="I144" s="12"/>
-      <c r="J144" s="12"/>
-      <c r="K144" s="12"/>
-      <c r="L144" s="11"/>
-      <c r="M144" s="11"/>
-    </row>
-    <row r="145" ht="33.0" customHeight="1">
-      <c r="A145" s="12"/>
-      <c r="B145" s="12"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11"/>
-      <c r="G145" s="12"/>
-      <c r="H145" s="12"/>
-      <c r="I145" s="12"/>
-      <c r="J145" s="12"/>
-      <c r="K145" s="12"/>
-      <c r="L145" s="11"/>
-      <c r="M145" s="11"/>
-    </row>
-    <row r="146" ht="33.0" customHeight="1">
-      <c r="A146" s="12"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="12"/>
-      <c r="H146" s="12"/>
-      <c r="I146" s="12"/>
-      <c r="J146" s="12"/>
-      <c r="K146" s="12"/>
-      <c r="L146" s="11"/>
-      <c r="M146" s="11"/>
-    </row>
-    <row r="147" ht="33.0" customHeight="1">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
-      <c r="G147" s="12"/>
-      <c r="H147" s="12"/>
-      <c r="I147" s="12"/>
-      <c r="J147" s="12"/>
-      <c r="K147" s="12"/>
-      <c r="L147" s="11"/>
-      <c r="M147" s="11"/>
-    </row>
-    <row r="148" ht="33.0" customHeight="1">
-      <c r="A148" s="12"/>
-      <c r="B148" s="12"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
-      <c r="G148" s="12"/>
-      <c r="H148" s="12"/>
-      <c r="I148" s="12"/>
-      <c r="J148" s="12"/>
-      <c r="K148" s="12"/>
-      <c r="L148" s="11"/>
-      <c r="M148" s="11"/>
-    </row>
-    <row r="149" ht="33.0" customHeight="1">
-      <c r="A149" s="12"/>
-      <c r="B149" s="12"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="12"/>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="12"/>
-      <c r="K149" s="12"/>
-      <c r="L149" s="11"/>
-      <c r="M149" s="11"/>
-    </row>
-    <row r="150" ht="33.0" customHeight="1">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="11"/>
-      <c r="F150" s="11"/>
-      <c r="G150" s="12"/>
-      <c r="H150" s="12"/>
-      <c r="I150" s="12"/>
-      <c r="J150" s="12"/>
-      <c r="K150" s="12"/>
-      <c r="L150" s="11"/>
-      <c r="M150" s="11"/>
-    </row>
-    <row r="151" ht="33.0" customHeight="1">
-      <c r="A151" s="12"/>
-      <c r="B151" s="12"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="11"/>
-      <c r="F151" s="11"/>
-      <c r="G151" s="12"/>
-      <c r="H151" s="12"/>
-      <c r="I151" s="12"/>
-      <c r="J151" s="12"/>
-      <c r="K151" s="12"/>
-      <c r="L151" s="11"/>
-      <c r="M151" s="11"/>
-    </row>
-    <row r="152" ht="33.0" customHeight="1">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="12"/>
-      <c r="H152" s="12"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="12"/>
-      <c r="K152" s="12"/>
-      <c r="L152" s="11"/>
-      <c r="M152" s="11"/>
-    </row>
-    <row r="153" ht="33.0" customHeight="1">
-      <c r="A153" s="12"/>
-      <c r="B153" s="12"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
-      <c r="G153" s="12"/>
-      <c r="H153" s="12"/>
-      <c r="I153" s="12"/>
-      <c r="J153" s="12"/>
-      <c r="K153" s="12"/>
-      <c r="L153" s="11"/>
-      <c r="M153" s="11"/>
-    </row>
-    <row r="154" ht="33.0" customHeight="1">
-      <c r="A154" s="12"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
-      <c r="G154" s="12"/>
-      <c r="H154" s="12"/>
-      <c r="I154" s="12"/>
-      <c r="J154" s="12"/>
-      <c r="K154" s="12"/>
-      <c r="L154" s="11"/>
-      <c r="M154" s="11"/>
-    </row>
-    <row r="155" ht="33.0" customHeight="1">
-      <c r="A155" s="12"/>
-      <c r="B155" s="12"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
-      <c r="G155" s="12"/>
-      <c r="H155" s="12"/>
-      <c r="I155" s="12"/>
-      <c r="J155" s="12"/>
-      <c r="K155" s="12"/>
-      <c r="L155" s="11"/>
-      <c r="M155" s="11"/>
-    </row>
-    <row r="156" ht="33.0" customHeight="1">
-      <c r="A156" s="12"/>
-      <c r="B156" s="12"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="12"/>
-      <c r="H156" s="12"/>
-      <c r="I156" s="12"/>
-      <c r="J156" s="12"/>
-      <c r="K156" s="12"/>
-      <c r="L156" s="11"/>
-      <c r="M156" s="11"/>
-    </row>
-    <row r="157" ht="33.0" customHeight="1">
-      <c r="A157" s="12"/>
-      <c r="B157" s="12"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="11"/>
-      <c r="G157" s="12"/>
-      <c r="H157" s="12"/>
-      <c r="I157" s="12"/>
-      <c r="J157" s="12"/>
-      <c r="K157" s="12"/>
-      <c r="L157" s="11"/>
-      <c r="M157" s="11"/>
-    </row>
-    <row r="158" ht="33.0" customHeight="1">
-      <c r="A158" s="12"/>
-      <c r="B158" s="12"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
-      <c r="F158" s="11"/>
-      <c r="G158" s="12"/>
-      <c r="H158" s="12"/>
-      <c r="I158" s="12"/>
-      <c r="J158" s="12"/>
-      <c r="K158" s="12"/>
-      <c r="L158" s="11"/>
-      <c r="M158" s="11"/>
-    </row>
-    <row r="159" ht="33.0" customHeight="1">
-      <c r="A159" s="12"/>
-      <c r="B159" s="12"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11"/>
-      <c r="G159" s="12"/>
-      <c r="H159" s="12"/>
-      <c r="I159" s="12"/>
-      <c r="J159" s="12"/>
-      <c r="K159" s="12"/>
-      <c r="L159" s="11"/>
-      <c r="M159" s="11"/>
-    </row>
-    <row r="160" ht="33.0" customHeight="1">
-      <c r="A160" s="12"/>
-      <c r="B160" s="12"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="12"/>
-      <c r="H160" s="12"/>
-      <c r="I160" s="12"/>
-      <c r="J160" s="12"/>
-      <c r="K160" s="12"/>
-      <c r="L160" s="11"/>
-      <c r="M160" s="11"/>
-    </row>
-    <row r="161" ht="33.0" customHeight="1">
-      <c r="A161" s="12"/>
-      <c r="B161" s="12"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
-      <c r="F161" s="11"/>
-      <c r="G161" s="12"/>
-      <c r="H161" s="12"/>
-      <c r="I161" s="12"/>
-      <c r="J161" s="12"/>
-      <c r="K161" s="12"/>
-      <c r="L161" s="11"/>
-      <c r="M161" s="11"/>
-    </row>
-    <row r="162" ht="33.0" customHeight="1">
-      <c r="A162" s="12"/>
-      <c r="B162" s="12"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
-      <c r="F162" s="11"/>
-      <c r="G162" s="12"/>
-      <c r="H162" s="12"/>
-      <c r="I162" s="12"/>
-      <c r="J162" s="12"/>
-      <c r="K162" s="12"/>
-      <c r="L162" s="11"/>
-      <c r="M162" s="11"/>
-    </row>
-    <row r="163" ht="33.0" customHeight="1">
-      <c r="A163" s="12"/>
-      <c r="B163" s="12"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
-      <c r="E163" s="11"/>
-      <c r="F163" s="11"/>
-      <c r="G163" s="12"/>
-      <c r="H163" s="12"/>
-      <c r="I163" s="12"/>
-      <c r="J163" s="12"/>
-      <c r="K163" s="12"/>
-      <c r="L163" s="11"/>
-      <c r="M163" s="11"/>
-    </row>
-    <row r="164" ht="33.0" customHeight="1">
-      <c r="A164" s="12"/>
-      <c r="B164" s="12"/>
-      <c r="C164" s="11"/>
-      <c r="D164" s="11"/>
-      <c r="E164" s="11"/>
-      <c r="F164" s="11"/>
-      <c r="G164" s="12"/>
-      <c r="H164" s="12"/>
-      <c r="I164" s="12"/>
-      <c r="J164" s="12"/>
-      <c r="K164" s="12"/>
-      <c r="L164" s="11"/>
-      <c r="M164" s="11"/>
-    </row>
-    <row r="165" ht="33.0" customHeight="1">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="11"/>
-      <c r="E165" s="11"/>
-      <c r="F165" s="11"/>
-      <c r="G165" s="12"/>
-      <c r="H165" s="12"/>
-      <c r="I165" s="12"/>
-      <c r="J165" s="12"/>
-      <c r="K165" s="12"/>
-      <c r="L165" s="11"/>
-      <c r="M165" s="11"/>
-    </row>
-    <row r="166" ht="33.0" customHeight="1">
-      <c r="A166" s="12"/>
-      <c r="B166" s="12"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="11"/>
-      <c r="E166" s="11"/>
-      <c r="F166" s="11"/>
-      <c r="G166" s="12"/>
-      <c r="H166" s="12"/>
-      <c r="I166" s="12"/>
-      <c r="J166" s="12"/>
-      <c r="K166" s="12"/>
-      <c r="L166" s="11"/>
-      <c r="M166" s="11"/>
-    </row>
-    <row r="167" ht="33.0" customHeight="1">
-      <c r="A167" s="12"/>
-      <c r="B167" s="12"/>
-      <c r="C167" s="11"/>
-      <c r="D167" s="11"/>
-      <c r="E167" s="11"/>
-      <c r="F167" s="11"/>
-      <c r="G167" s="12"/>
-      <c r="H167" s="12"/>
-      <c r="I167" s="12"/>
-      <c r="J167" s="12"/>
-      <c r="K167" s="12"/>
-      <c r="L167" s="11"/>
-      <c r="M167" s="11"/>
-    </row>
-    <row r="168" ht="33.0" customHeight="1">
-      <c r="A168" s="12"/>
-      <c r="B168" s="12"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="11"/>
-      <c r="E168" s="11"/>
-      <c r="F168" s="11"/>
-      <c r="G168" s="12"/>
-      <c r="H168" s="12"/>
-      <c r="I168" s="12"/>
-      <c r="J168" s="12"/>
-      <c r="K168" s="12"/>
-      <c r="L168" s="11"/>
-      <c r="M168" s="11"/>
-    </row>
-    <row r="169" ht="33.0" customHeight="1">
-      <c r="A169" s="12"/>
-      <c r="B169" s="12"/>
-      <c r="C169" s="11"/>
-      <c r="D169" s="11"/>
-      <c r="E169" s="11"/>
-      <c r="F169" s="11"/>
-      <c r="G169" s="12"/>
-      <c r="H169" s="12"/>
-      <c r="I169" s="12"/>
-      <c r="J169" s="12"/>
-      <c r="K169" s="12"/>
-      <c r="L169" s="11"/>
-      <c r="M169" s="11"/>
-    </row>
-    <row r="170" ht="33.0" customHeight="1">
-      <c r="A170" s="12"/>
-      <c r="B170" s="12"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="11"/>
-      <c r="E170" s="11"/>
-      <c r="F170" s="11"/>
-      <c r="G170" s="12"/>
-      <c r="H170" s="12"/>
-      <c r="I170" s="12"/>
-      <c r="J170" s="12"/>
-      <c r="K170" s="12"/>
-      <c r="L170" s="11"/>
-      <c r="M170" s="11"/>
-    </row>
-    <row r="171" ht="33.0" customHeight="1">
-      <c r="A171" s="12"/>
-      <c r="B171" s="12"/>
-      <c r="C171" s="11"/>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
-      <c r="F171" s="11"/>
-      <c r="G171" s="12"/>
-      <c r="H171" s="12"/>
-      <c r="I171" s="12"/>
-      <c r="J171" s="12"/>
-      <c r="K171" s="12"/>
-      <c r="L171" s="11"/>
-      <c r="M171" s="11"/>
-    </row>
-    <row r="172" ht="33.0" customHeight="1">
-      <c r="A172" s="12"/>
-      <c r="B172" s="12"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="11"/>
-      <c r="E172" s="11"/>
-      <c r="F172" s="11"/>
-      <c r="G172" s="12"/>
-      <c r="H172" s="12"/>
-      <c r="I172" s="12"/>
-      <c r="J172" s="12"/>
-      <c r="K172" s="12"/>
-      <c r="L172" s="11"/>
-      <c r="M172" s="11"/>
-    </row>
-    <row r="173" ht="33.0" customHeight="1">
-      <c r="A173" s="12"/>
-      <c r="B173" s="12"/>
-      <c r="C173" s="11"/>
-      <c r="D173" s="11"/>
-      <c r="E173" s="11"/>
-      <c r="F173" s="11"/>
-      <c r="G173" s="12"/>
-      <c r="H173" s="12"/>
-      <c r="I173" s="12"/>
-      <c r="J173" s="12"/>
-      <c r="K173" s="12"/>
-      <c r="L173" s="11"/>
-      <c r="M173" s="11"/>
-    </row>
-    <row r="174" ht="33.0" customHeight="1">
-      <c r="A174" s="12"/>
-      <c r="B174" s="12"/>
-      <c r="C174" s="11"/>
-      <c r="D174" s="11"/>
-      <c r="E174" s="11"/>
-      <c r="F174" s="11"/>
-      <c r="G174" s="12"/>
-      <c r="H174" s="12"/>
-      <c r="I174" s="12"/>
-      <c r="J174" s="12"/>
-      <c r="K174" s="12"/>
-      <c r="L174" s="11"/>
-      <c r="M174" s="11"/>
-    </row>
-    <row r="175" ht="33.0" customHeight="1">
-      <c r="A175" s="12"/>
-      <c r="B175" s="12"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="11"/>
-      <c r="E175" s="11"/>
-      <c r="F175" s="11"/>
-      <c r="G175" s="12"/>
-      <c r="H175" s="12"/>
-      <c r="I175" s="12"/>
-      <c r="J175" s="12"/>
-      <c r="K175" s="12"/>
-      <c r="L175" s="11"/>
-      <c r="M175" s="11"/>
-    </row>
-    <row r="176" ht="33.0" customHeight="1">
-      <c r="A176" s="12"/>
-      <c r="B176" s="12"/>
-      <c r="C176" s="11"/>
-      <c r="D176" s="11"/>
-      <c r="E176" s="11"/>
-      <c r="F176" s="11"/>
-      <c r="G176" s="12"/>
-      <c r="H176" s="12"/>
-      <c r="I176" s="12"/>
-      <c r="J176" s="12"/>
-      <c r="K176" s="12"/>
-      <c r="L176" s="11"/>
-      <c r="M176" s="11"/>
-    </row>
-    <row r="177" ht="33.0" customHeight="1">
-      <c r="A177" s="12"/>
-      <c r="B177" s="12"/>
-      <c r="C177" s="11"/>
-      <c r="D177" s="11"/>
-      <c r="E177" s="11"/>
-      <c r="F177" s="11"/>
-      <c r="G177" s="12"/>
-      <c r="H177" s="12"/>
-      <c r="I177" s="12"/>
-      <c r="J177" s="12"/>
-      <c r="K177" s="12"/>
-      <c r="L177" s="11"/>
-      <c r="M177" s="11"/>
-    </row>
-    <row r="178" ht="33.0" customHeight="1">
-      <c r="A178" s="12"/>
-      <c r="B178" s="12"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
-      <c r="E178" s="11"/>
-      <c r="F178" s="11"/>
-      <c r="G178" s="12"/>
-      <c r="H178" s="12"/>
-      <c r="I178" s="12"/>
-      <c r="J178" s="12"/>
-      <c r="K178" s="12"/>
-      <c r="L178" s="11"/>
-      <c r="M178" s="11"/>
-    </row>
-    <row r="179" ht="33.0" customHeight="1">
-      <c r="A179" s="12"/>
-      <c r="B179" s="12"/>
-      <c r="C179" s="11"/>
-      <c r="D179" s="11"/>
-      <c r="E179" s="11"/>
-      <c r="F179" s="11"/>
-      <c r="G179" s="12"/>
-      <c r="H179" s="12"/>
-      <c r="I179" s="12"/>
-      <c r="J179" s="12"/>
-      <c r="K179" s="12"/>
-      <c r="L179" s="11"/>
-      <c r="M179" s="11"/>
-    </row>
-    <row r="180" ht="33.0" customHeight="1">
-      <c r="A180" s="12"/>
-      <c r="B180" s="12"/>
-      <c r="C180" s="11"/>
-      <c r="D180" s="11"/>
-      <c r="E180" s="11"/>
-      <c r="F180" s="11"/>
-      <c r="G180" s="12"/>
-      <c r="H180" s="12"/>
-      <c r="I180" s="12"/>
-      <c r="J180" s="12"/>
-      <c r="K180" s="12"/>
-      <c r="L180" s="11"/>
-      <c r="M180" s="11"/>
-    </row>
-    <row r="181" ht="33.0" customHeight="1">
-      <c r="A181" s="12"/>
-      <c r="B181" s="12"/>
-      <c r="C181" s="11"/>
-      <c r="D181" s="11"/>
-      <c r="E181" s="11"/>
-      <c r="F181" s="11"/>
-      <c r="G181" s="12"/>
-      <c r="H181" s="12"/>
-      <c r="I181" s="12"/>
-      <c r="J181" s="12"/>
-      <c r="K181" s="12"/>
-      <c r="L181" s="11"/>
-      <c r="M181" s="11"/>
-    </row>
-    <row r="182" ht="33.0" customHeight="1">
-      <c r="A182" s="12"/>
-      <c r="B182" s="12"/>
-      <c r="C182" s="11"/>
-      <c r="D182" s="11"/>
-      <c r="E182" s="11"/>
-      <c r="F182" s="11"/>
-      <c r="G182" s="12"/>
-      <c r="H182" s="12"/>
-      <c r="I182" s="12"/>
-      <c r="J182" s="12"/>
-      <c r="K182" s="12"/>
-      <c r="L182" s="11"/>
-      <c r="M182" s="11"/>
-    </row>
-    <row r="183" ht="33.0" customHeight="1">
-      <c r="A183" s="12"/>
-      <c r="B183" s="12"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="11"/>
-      <c r="E183" s="11"/>
-      <c r="F183" s="11"/>
-      <c r="G183" s="12"/>
-      <c r="H183" s="12"/>
-      <c r="I183" s="12"/>
-      <c r="J183" s="12"/>
-      <c r="K183" s="12"/>
-      <c r="L183" s="11"/>
-      <c r="M183" s="11"/>
-    </row>
-    <row r="184" ht="33.0" customHeight="1">
-      <c r="A184" s="12"/>
-      <c r="B184" s="12"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="11"/>
-      <c r="E184" s="11"/>
-      <c r="F184" s="11"/>
-      <c r="G184" s="12"/>
-      <c r="H184" s="12"/>
-      <c r="I184" s="12"/>
-      <c r="J184" s="12"/>
-      <c r="K184" s="12"/>
-      <c r="L184" s="11"/>
-      <c r="M184" s="11"/>
-    </row>
-    <row r="185" ht="33.0" customHeight="1">
-      <c r="A185" s="12"/>
-      <c r="B185" s="12"/>
-      <c r="C185" s="11"/>
-      <c r="D185" s="11"/>
-      <c r="E185" s="11"/>
-      <c r="F185" s="11"/>
-      <c r="G185" s="12"/>
-      <c r="H185" s="12"/>
-      <c r="I185" s="12"/>
-      <c r="J185" s="12"/>
-      <c r="K185" s="12"/>
-      <c r="L185" s="11"/>
-      <c r="M185" s="11"/>
-    </row>
-    <row r="186" ht="33.0" customHeight="1">
-      <c r="A186" s="12"/>
-      <c r="B186" s="12"/>
-      <c r="C186" s="11"/>
-      <c r="D186" s="11"/>
-      <c r="E186" s="11"/>
-      <c r="F186" s="11"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="12"/>
-      <c r="I186" s="12"/>
-      <c r="J186" s="12"/>
-      <c r="K186" s="12"/>
-      <c r="L186" s="11"/>
-      <c r="M186" s="11"/>
-    </row>
-    <row r="187" ht="33.0" customHeight="1">
-      <c r="A187" s="12"/>
-      <c r="B187" s="12"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="11"/>
-      <c r="E187" s="11"/>
-      <c r="F187" s="11"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="12"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="12"/>
-      <c r="K187" s="12"/>
-      <c r="L187" s="11"/>
-      <c r="M187" s="11"/>
-    </row>
-    <row r="188" ht="33.0" customHeight="1">
-      <c r="A188" s="12"/>
-      <c r="B188" s="12"/>
-      <c r="C188" s="11"/>
-      <c r="D188" s="11"/>
-      <c r="E188" s="11"/>
-      <c r="F188" s="11"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="12"/>
-      <c r="I188" s="12"/>
-      <c r="J188" s="12"/>
-      <c r="K188" s="12"/>
-      <c r="L188" s="11"/>
-      <c r="M188" s="11"/>
-    </row>
-    <row r="189" ht="33.0" customHeight="1">
-      <c r="A189" s="12"/>
-      <c r="B189" s="12"/>
-      <c r="C189" s="11"/>
-      <c r="D189" s="11"/>
-      <c r="E189" s="11"/>
-      <c r="F189" s="11"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="12"/>
-      <c r="I189" s="12"/>
-      <c r="J189" s="12"/>
-      <c r="K189" s="12"/>
-      <c r="L189" s="11"/>
-      <c r="M189" s="11"/>
-    </row>
-    <row r="190" ht="33.0" customHeight="1">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-      <c r="C190" s="11"/>
-      <c r="D190" s="11"/>
-      <c r="E190" s="11"/>
-      <c r="F190" s="11"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="12"/>
-      <c r="I190" s="12"/>
-      <c r="J190" s="12"/>
-      <c r="K190" s="12"/>
-      <c r="L190" s="11"/>
-      <c r="M190" s="11"/>
-    </row>
-    <row r="191" ht="33.0" customHeight="1">
-      <c r="A191" s="12"/>
-      <c r="B191" s="12"/>
-      <c r="C191" s="11"/>
-      <c r="D191" s="11"/>
-      <c r="E191" s="11"/>
-      <c r="F191" s="11"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="12"/>
-      <c r="I191" s="12"/>
-      <c r="J191" s="12"/>
-      <c r="K191" s="12"/>
-      <c r="L191" s="11"/>
-      <c r="M191" s="11"/>
-    </row>
-    <row r="192" ht="33.0" customHeight="1">
-      <c r="A192" s="12"/>
-      <c r="B192" s="12"/>
-      <c r="C192" s="11"/>
-      <c r="D192" s="11"/>
-      <c r="E192" s="11"/>
-      <c r="F192" s="11"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="12"/>
-      <c r="I192" s="12"/>
-      <c r="J192" s="12"/>
-      <c r="K192" s="12"/>
-      <c r="L192" s="11"/>
-      <c r="M192" s="11"/>
-    </row>
-    <row r="193" ht="33.0" customHeight="1">
-      <c r="A193" s="12"/>
-      <c r="B193" s="12"/>
-      <c r="C193" s="11"/>
-      <c r="D193" s="11"/>
-      <c r="E193" s="11"/>
-      <c r="F193" s="11"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="12"/>
-      <c r="I193" s="12"/>
-      <c r="J193" s="12"/>
-      <c r="K193" s="12"/>
-      <c r="L193" s="11"/>
-      <c r="M193" s="11"/>
-    </row>
-    <row r="194" ht="33.0" customHeight="1">
-      <c r="A194" s="12"/>
-      <c r="B194" s="12"/>
-      <c r="C194" s="11"/>
-      <c r="D194" s="11"/>
-      <c r="E194" s="11"/>
-      <c r="F194" s="11"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="12"/>
-      <c r="I194" s="12"/>
-      <c r="J194" s="12"/>
-      <c r="K194" s="12"/>
-      <c r="L194" s="11"/>
-      <c r="M194" s="11"/>
-    </row>
-    <row r="195" ht="33.0" customHeight="1">
-      <c r="A195" s="12"/>
-      <c r="B195" s="12"/>
-      <c r="C195" s="11"/>
-      <c r="D195" s="11"/>
-      <c r="E195" s="11"/>
-      <c r="F195" s="11"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="12"/>
-      <c r="I195" s="12"/>
-      <c r="J195" s="12"/>
-      <c r="K195" s="12"/>
-      <c r="L195" s="11"/>
-      <c r="M195" s="11"/>
-    </row>
-    <row r="196" ht="33.0" customHeight="1">
-      <c r="A196" s="12"/>
-      <c r="B196" s="12"/>
-      <c r="C196" s="11"/>
-      <c r="D196" s="11"/>
-      <c r="E196" s="11"/>
-      <c r="F196" s="11"/>
-      <c r="G196" s="12"/>
-      <c r="H196" s="12"/>
-      <c r="I196" s="12"/>
-      <c r="J196" s="12"/>
-      <c r="K196" s="12"/>
-      <c r="L196" s="11"/>
-      <c r="M196" s="11"/>
-    </row>
-    <row r="197" ht="33.0" customHeight="1">
-      <c r="A197" s="12"/>
-      <c r="B197" s="12"/>
-      <c r="C197" s="11"/>
-      <c r="D197" s="11"/>
-      <c r="E197" s="11"/>
-      <c r="F197" s="11"/>
-      <c r="G197" s="12"/>
-      <c r="H197" s="12"/>
-      <c r="I197" s="12"/>
-      <c r="J197" s="12"/>
-      <c r="K197" s="12"/>
-      <c r="L197" s="11"/>
-      <c r="M197" s="11"/>
-    </row>
-    <row r="198" ht="33.0" customHeight="1">
-      <c r="A198" s="12"/>
-      <c r="B198" s="12"/>
-      <c r="C198" s="11"/>
-      <c r="D198" s="11"/>
-      <c r="E198" s="11"/>
-      <c r="F198" s="11"/>
-      <c r="G198" s="12"/>
-      <c r="H198" s="12"/>
-      <c r="I198" s="12"/>
-      <c r="J198" s="12"/>
-      <c r="K198" s="12"/>
-      <c r="L198" s="11"/>
-      <c r="M198" s="11"/>
-    </row>
-    <row r="199" ht="33.0" customHeight="1">
-      <c r="A199" s="12"/>
-      <c r="B199" s="12"/>
-      <c r="C199" s="11"/>
-      <c r="D199" s="11"/>
-      <c r="E199" s="11"/>
-      <c r="F199" s="11"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="12"/>
-      <c r="I199" s="12"/>
-      <c r="J199" s="12"/>
-      <c r="K199" s="12"/>
-      <c r="L199" s="11"/>
-      <c r="M199" s="11"/>
-    </row>
-    <row r="200" ht="33.0" customHeight="1">
-      <c r="A200" s="12"/>
-      <c r="B200" s="12"/>
-      <c r="C200" s="11"/>
-      <c r="D200" s="11"/>
-      <c r="E200" s="11"/>
-      <c r="F200" s="11"/>
-      <c r="G200" s="12"/>
-      <c r="H200" s="12"/>
-      <c r="I200" s="12"/>
-      <c r="J200" s="12"/>
-      <c r="K200" s="12"/>
-      <c r="L200" s="11"/>
-      <c r="M200" s="11"/>
-    </row>
-    <row r="201" ht="33.0" customHeight="1">
-      <c r="A201" s="12"/>
-      <c r="B201" s="12"/>
-      <c r="C201" s="11"/>
-      <c r="D201" s="11"/>
-      <c r="E201" s="11"/>
-      <c r="F201" s="11"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="12"/>
-      <c r="I201" s="12"/>
-      <c r="J201" s="12"/>
-      <c r="K201" s="12"/>
-      <c r="L201" s="11"/>
-      <c r="M201" s="11"/>
-    </row>
-    <row r="202" ht="13.5" customHeight="1"/>
-    <row r="203" ht="13.5" customHeight="1"/>
-    <row r="204" ht="13.5" customHeight="1"/>
-    <row r="205" ht="13.5" customHeight="1"/>
-    <row r="206" ht="13.5" customHeight="1"/>
-    <row r="207" ht="13.5" customHeight="1"/>
-    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="106" spans="1:13" ht="33" customHeight="1">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+    </row>
+    <row r="107" spans="1:13" ht="33" customHeight="1">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+    </row>
+    <row r="108" spans="1:13" ht="33" customHeight="1">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+    </row>
+    <row r="109" spans="1:13" ht="33" customHeight="1">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+    </row>
+    <row r="110" spans="1:13" ht="33" customHeight="1">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+    </row>
+    <row r="111" spans="1:13" ht="33" customHeight="1">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+    </row>
+    <row r="112" spans="1:13" ht="33" customHeight="1">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+    </row>
+    <row r="113" spans="1:13" ht="33" customHeight="1">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+    </row>
+    <row r="114" spans="1:13" ht="33" customHeight="1">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+    </row>
+    <row r="115" spans="1:13" ht="33" customHeight="1">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+    </row>
+    <row r="116" spans="1:13" ht="33" customHeight="1">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+    </row>
+    <row r="117" spans="1:13" ht="33" customHeight="1">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+    </row>
+    <row r="118" spans="1:13" ht="33" customHeight="1">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+    </row>
+    <row r="119" spans="1:13" ht="33" customHeight="1">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+    </row>
+    <row r="120" spans="1:13" ht="33" customHeight="1">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+    </row>
+    <row r="121" spans="1:13" ht="33" customHeight="1">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+    </row>
+    <row r="122" spans="1:13" ht="33" customHeight="1">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+    </row>
+    <row r="123" spans="1:13" ht="33" customHeight="1">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+    </row>
+    <row r="124" spans="1:13" ht="33" customHeight="1">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+    </row>
+    <row r="125" spans="1:13" ht="33" customHeight="1">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+    </row>
+    <row r="126" spans="1:13" ht="33" customHeight="1">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+    </row>
+    <row r="127" spans="1:13" ht="33" customHeight="1">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+    </row>
+    <row r="128" spans="1:13" ht="33" customHeight="1">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="4"/>
+      <c r="M128" s="4"/>
+    </row>
+    <row r="129" spans="1:13" ht="33" customHeight="1">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+    </row>
+    <row r="130" spans="1:13" ht="33" customHeight="1">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="4"/>
+      <c r="M130" s="4"/>
+    </row>
+    <row r="131" spans="1:13" ht="33" customHeight="1">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="4"/>
+      <c r="M131" s="4"/>
+    </row>
+    <row r="132" spans="1:13" ht="33" customHeight="1">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="4"/>
+      <c r="M132" s="4"/>
+    </row>
+    <row r="133" spans="1:13" ht="33" customHeight="1">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="4"/>
+      <c r="M133" s="4"/>
+    </row>
+    <row r="134" spans="1:13" ht="33" customHeight="1">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4"/>
+    </row>
+    <row r="135" spans="1:13" ht="33" customHeight="1">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="4"/>
+      <c r="M135" s="4"/>
+    </row>
+    <row r="136" spans="1:13" ht="33" customHeight="1">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="4"/>
+      <c r="M136" s="4"/>
+    </row>
+    <row r="137" spans="1:13" ht="33" customHeight="1">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3"/>
+      <c r="L137" s="4"/>
+      <c r="M137" s="4"/>
+    </row>
+    <row r="138" spans="1:13" ht="33" customHeight="1">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+    </row>
+    <row r="139" spans="1:13" ht="33" customHeight="1">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+    </row>
+    <row r="140" spans="1:13" ht="33" customHeight="1">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="4"/>
+      <c r="M140" s="4"/>
+    </row>
+    <row r="141" spans="1:13" ht="33" customHeight="1">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="4"/>
+      <c r="M141" s="4"/>
+    </row>
+    <row r="142" spans="1:13" ht="33" customHeight="1">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="4"/>
+      <c r="M142" s="4"/>
+    </row>
+    <row r="143" spans="1:13" ht="33" customHeight="1">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="4"/>
+      <c r="M143" s="4"/>
+    </row>
+    <row r="144" spans="1:13" ht="33" customHeight="1">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="4"/>
+      <c r="M144" s="4"/>
+    </row>
+    <row r="145" spans="1:13" ht="33" customHeight="1">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3"/>
+      <c r="L145" s="4"/>
+      <c r="M145" s="4"/>
+    </row>
+    <row r="146" spans="1:13" ht="33" customHeight="1">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
+      <c r="L146" s="4"/>
+      <c r="M146" s="4"/>
+    </row>
+    <row r="147" spans="1:13" ht="33" customHeight="1">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="4"/>
+      <c r="M147" s="4"/>
+    </row>
+    <row r="148" spans="1:13" ht="33" customHeight="1">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="3"/>
+      <c r="K148" s="3"/>
+      <c r="L148" s="4"/>
+      <c r="M148" s="4"/>
+    </row>
+    <row r="149" spans="1:13" ht="33" customHeight="1">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3"/>
+      <c r="K149" s="3"/>
+      <c r="L149" s="4"/>
+      <c r="M149" s="4"/>
+    </row>
+    <row r="150" spans="1:13" ht="33" customHeight="1">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+      <c r="L150" s="4"/>
+      <c r="M150" s="4"/>
+    </row>
+    <row r="151" spans="1:13" ht="33" customHeight="1">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="4"/>
+      <c r="M151" s="4"/>
+    </row>
+    <row r="152" spans="1:13" ht="33" customHeight="1">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="4"/>
+      <c r="M152" s="4"/>
+    </row>
+    <row r="153" spans="1:13" ht="33" customHeight="1">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+    </row>
+    <row r="154" spans="1:13" ht="33" customHeight="1">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="3"/>
+      <c r="K154" s="3"/>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+    </row>
+    <row r="155" spans="1:13" ht="33" customHeight="1">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="4"/>
+      <c r="M155" s="4"/>
+    </row>
+    <row r="156" spans="1:13" ht="33" customHeight="1">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3"/>
+      <c r="K156" s="3"/>
+      <c r="L156" s="4"/>
+      <c r="M156" s="4"/>
+    </row>
+    <row r="157" spans="1:13" ht="33" customHeight="1">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="4"/>
+      <c r="M157" s="4"/>
+    </row>
+    <row r="158" spans="1:13" ht="33" customHeight="1">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3"/>
+      <c r="L158" s="4"/>
+      <c r="M158" s="4"/>
+    </row>
+    <row r="159" spans="1:13" ht="33" customHeight="1">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="3"/>
+      <c r="K159" s="3"/>
+      <c r="L159" s="4"/>
+      <c r="M159" s="4"/>
+    </row>
+    <row r="160" spans="1:13" ht="33" customHeight="1">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="3"/>
+      <c r="L160" s="4"/>
+      <c r="M160" s="4"/>
+    </row>
+    <row r="161" spans="1:13" ht="33" customHeight="1">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="3"/>
+      <c r="K161" s="3"/>
+      <c r="L161" s="4"/>
+      <c r="M161" s="4"/>
+    </row>
+    <row r="162" spans="1:13" ht="33" customHeight="1">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="4"/>
+      <c r="M162" s="4"/>
+    </row>
+    <row r="163" spans="1:13" ht="33" customHeight="1">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="3"/>
+      <c r="K163" s="3"/>
+      <c r="L163" s="4"/>
+      <c r="M163" s="4"/>
+    </row>
+    <row r="164" spans="1:13" ht="33" customHeight="1">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="4"/>
+      <c r="M164" s="4"/>
+    </row>
+    <row r="165" spans="1:13" ht="33" customHeight="1">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="4"/>
+      <c r="M165" s="4"/>
+    </row>
+    <row r="166" spans="1:13" ht="33" customHeight="1">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="4"/>
+      <c r="M166" s="4"/>
+    </row>
+    <row r="167" spans="1:13" ht="33" customHeight="1">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="4"/>
+      <c r="M167" s="4"/>
+    </row>
+    <row r="168" spans="1:13" ht="33" customHeight="1">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="4"/>
+      <c r="M168" s="4"/>
+    </row>
+    <row r="169" spans="1:13" ht="33" customHeight="1">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="4"/>
+      <c r="M169" s="4"/>
+    </row>
+    <row r="170" spans="1:13" ht="33" customHeight="1">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="3"/>
+      <c r="J170" s="3"/>
+      <c r="K170" s="3"/>
+      <c r="L170" s="4"/>
+      <c r="M170" s="4"/>
+    </row>
+    <row r="171" spans="1:13" ht="33" customHeight="1">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="3"/>
+      <c r="J171" s="3"/>
+      <c r="K171" s="3"/>
+      <c r="L171" s="4"/>
+      <c r="M171" s="4"/>
+    </row>
+    <row r="172" spans="1:13" ht="33" customHeight="1">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="4"/>
+      <c r="M172" s="4"/>
+    </row>
+    <row r="173" spans="1:13" ht="33" customHeight="1">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="4"/>
+      <c r="M173" s="4"/>
+    </row>
+    <row r="174" spans="1:13" ht="33" customHeight="1">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="4"/>
+      <c r="M174" s="4"/>
+    </row>
+    <row r="175" spans="1:13" ht="33" customHeight="1">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="3"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="4"/>
+      <c r="M175" s="4"/>
+    </row>
+    <row r="176" spans="1:13" ht="33" customHeight="1">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3"/>
+      <c r="J176" s="3"/>
+      <c r="K176" s="3"/>
+      <c r="L176" s="4"/>
+      <c r="M176" s="4"/>
+    </row>
+    <row r="177" spans="1:13" ht="33" customHeight="1">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="3"/>
+      <c r="J177" s="3"/>
+      <c r="K177" s="3"/>
+      <c r="L177" s="4"/>
+      <c r="M177" s="4"/>
+    </row>
+    <row r="178" spans="1:13" ht="33" customHeight="1">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+      <c r="J178" s="3"/>
+      <c r="K178" s="3"/>
+      <c r="L178" s="4"/>
+      <c r="M178" s="4"/>
+    </row>
+    <row r="179" spans="1:13" ht="33" customHeight="1">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="3"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="4"/>
+      <c r="M179" s="4"/>
+    </row>
+    <row r="180" spans="1:13" ht="33" customHeight="1">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="4"/>
+      <c r="M180" s="4"/>
+    </row>
+    <row r="181" spans="1:13" ht="33" customHeight="1">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="4"/>
+      <c r="M181" s="4"/>
+    </row>
+    <row r="182" spans="1:13" ht="33" customHeight="1">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="4"/>
+      <c r="M182" s="4"/>
+    </row>
+    <row r="183" spans="1:13" ht="33" customHeight="1">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="3"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="4"/>
+      <c r="M183" s="4"/>
+    </row>
+    <row r="184" spans="1:13" ht="33" customHeight="1">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="4"/>
+      <c r="M184" s="4"/>
+    </row>
+    <row r="185" spans="1:13" ht="33" customHeight="1">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="J185" s="3"/>
+      <c r="K185" s="3"/>
+      <c r="L185" s="4"/>
+      <c r="M185" s="4"/>
+    </row>
+    <row r="186" spans="1:13" ht="33" customHeight="1">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4"/>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="J186" s="3"/>
+      <c r="K186" s="3"/>
+      <c r="L186" s="4"/>
+      <c r="M186" s="4"/>
+    </row>
+    <row r="187" spans="1:13" ht="33" customHeight="1">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="J187" s="3"/>
+      <c r="K187" s="3"/>
+      <c r="L187" s="4"/>
+      <c r="M187" s="4"/>
+    </row>
+    <row r="188" spans="1:13" ht="33" customHeight="1">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="J188" s="3"/>
+      <c r="K188" s="3"/>
+      <c r="L188" s="4"/>
+      <c r="M188" s="4"/>
+    </row>
+    <row r="189" spans="1:13" ht="33" customHeight="1">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="J189" s="3"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="4"/>
+      <c r="M189" s="4"/>
+    </row>
+    <row r="190" spans="1:13" ht="33" customHeight="1">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="3"/>
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+      <c r="J190" s="3"/>
+      <c r="K190" s="3"/>
+      <c r="L190" s="4"/>
+      <c r="M190" s="4"/>
+    </row>
+    <row r="191" spans="1:13" ht="33" customHeight="1">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="3"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="4"/>
+      <c r="M191" s="4"/>
+    </row>
+    <row r="192" spans="1:13" ht="33" customHeight="1">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="4"/>
+      <c r="M192" s="4"/>
+    </row>
+    <row r="193" spans="1:13" ht="33" customHeight="1">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+      <c r="J193" s="3"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="4"/>
+      <c r="M193" s="4"/>
+    </row>
+    <row r="194" spans="1:13" ht="33" customHeight="1">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+      <c r="G194" s="3"/>
+      <c r="H194" s="3"/>
+      <c r="I194" s="3"/>
+      <c r="J194" s="3"/>
+      <c r="K194" s="3"/>
+      <c r="L194" s="4"/>
+      <c r="M194" s="4"/>
+    </row>
+    <row r="195" spans="1:13" ht="33" customHeight="1">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+      <c r="I195" s="3"/>
+      <c r="J195" s="3"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="4"/>
+      <c r="M195" s="4"/>
+    </row>
+    <row r="196" spans="1:13" ht="33" customHeight="1">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+      <c r="I196" s="3"/>
+      <c r="J196" s="3"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="4"/>
+      <c r="M196" s="4"/>
+    </row>
+    <row r="197" spans="1:13" ht="33" customHeight="1">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
+      <c r="I197" s="3"/>
+      <c r="J197" s="3"/>
+      <c r="K197" s="3"/>
+      <c r="L197" s="4"/>
+      <c r="M197" s="4"/>
+    </row>
+    <row r="198" spans="1:13" ht="33" customHeight="1">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+      <c r="I198" s="3"/>
+      <c r="J198" s="3"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="4"/>
+      <c r="M198" s="4"/>
+    </row>
+    <row r="199" spans="1:13" ht="33" customHeight="1">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
+      <c r="I199" s="3"/>
+      <c r="J199" s="3"/>
+      <c r="K199" s="3"/>
+      <c r="L199" s="4"/>
+      <c r="M199" s="4"/>
+    </row>
+    <row r="200" spans="1:13" ht="33" customHeight="1">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="4"/>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+      <c r="G200" s="3"/>
+      <c r="H200" s="3"/>
+      <c r="I200" s="3"/>
+      <c r="J200" s="3"/>
+      <c r="K200" s="3"/>
+      <c r="L200" s="4"/>
+      <c r="M200" s="4"/>
+    </row>
+    <row r="201" spans="1:13" ht="33" customHeight="1">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+      <c r="G201" s="3"/>
+      <c r="H201" s="3"/>
+      <c r="I201" s="3"/>
+      <c r="J201" s="3"/>
+      <c r="K201" s="3"/>
+      <c r="L201" s="4"/>
+      <c r="M201" s="4"/>
+    </row>
+    <row r="202" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="203" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="204" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="205" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="206" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="207" spans="1:13" ht="13.5" customHeight="1"/>
+    <row r="208" spans="1:13" ht="13.5" customHeight="1"/>
     <row r="209" ht="13.5" customHeight="1"/>
     <row r="210" ht="13.5" customHeight="1"/>
     <row r="211" ht="13.5" customHeight="1"/>
@@ -11467,65 +11538,62 @@
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="G2:G201">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>G2="Alta"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G201">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>G2="Media"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G201">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>G2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J201">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>J2="Finalizada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J201">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>J2="Bloqueada"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>K2="Aprobada"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>K2="Con observaciones"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K201">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>K2="Rechazada"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B201">
-      <formula1>Epicas!$B$2:$B$98</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G201">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G201" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K201">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K201" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Pendiente,Aprobada,Con observaciones,Rechazada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J201">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J201" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"Pendiente,En análisis,Lista,En desarrollo,En revisión,Finalizada,Bloqueada"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Epicas!$B$2:$B$98</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B201</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>